--- a/documentation/Systems Develpoment GANTT CHART.xlsx
+++ b/documentation/Systems Develpoment GANTT CHART.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uweacuk-my.sharepoint.com/personal/hasaan2_ahmad_live_uwe_ac_uk/Documents/BSc Computer Science/BSC CS YEAR 2/Systems Development - Group Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1119" documentId="11_3C4179B01545E19DD6C385890107473B0B440F85" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{925078D1-8D9D-4ED3-9494-DADA7E987E16}"/>
+  <xr:revisionPtr revIDLastSave="1126" documentId="11_3C4179B01545E19DD6C385890107473B0B440F85" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28ABD61D-D402-48E1-8A1E-A069C71E3300}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project schedule" sheetId="11" r:id="rId1"/>
@@ -314,7 +314,7 @@
     <t>Display Top 3 Products</t>
   </si>
   <si>
-    <t>System must show most-sold 3 foods &amp; 3 coffees in chart, auto-updating for last 4 weeks, by Week 5.</t>
+    <t>System must show most-sold Croissant (1 class) &amp; Coffee (2 classes) in chart, auto-updating for last 4 weeks, by Week 5.</t>
   </si>
   <si>
     <t>Correct bar/line chart; validated against dataset.</t>
@@ -518,7 +518,7 @@
     <t>Objective 2 - Specific</t>
   </si>
   <si>
-    <t>Design and implement an interactive dashboard displaying historical sales trends for the top 3 food items and top 3 coffee products using appropriate graphical representations</t>
+    <t>Design and implement an interactive dashboard displaying historical sales trends for the food items and top coffee products (of the 2 available) using appropriate graphical representations</t>
   </si>
   <si>
     <t>Verification: Dashboard renders all 6 charts; peer review feedback form completed</t>
@@ -2120,6 +2120,45 @@
     <xf numFmtId="0" fontId="25" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2176,45 +2215,6 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -3131,54 +3131,54 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="J1" s="1"/>
-      <c r="K1" s="173" t="s">
+      <c r="K1" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="173"/>
-      <c r="M1" s="173"/>
-      <c r="N1" s="173"/>
-      <c r="O1" s="173"/>
-      <c r="P1" s="173"/>
-      <c r="Q1" s="173"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="148"/>
+      <c r="P1" s="148"/>
+      <c r="Q1" s="148"/>
       <c r="R1" s="48"/>
-      <c r="S1" s="172">
+      <c r="S1" s="149">
         <f ca="1">TODAY()</f>
         <v>45984</v>
       </c>
-      <c r="T1" s="172"/>
-      <c r="U1" s="172"/>
-      <c r="V1" s="172"/>
-      <c r="W1" s="172"/>
-      <c r="X1" s="172"/>
-      <c r="Y1" s="172"/>
-      <c r="Z1" s="172"/>
-      <c r="AA1" s="172"/>
-      <c r="AB1" s="172"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="149"/>
+      <c r="W1" s="149"/>
+      <c r="X1" s="149"/>
+      <c r="Y1" s="149"/>
+      <c r="Z1" s="149"/>
+      <c r="AA1" s="149"/>
+      <c r="AB1" s="149"/>
       <c r="AC1" s="49"/>
       <c r="AD1" s="49"/>
-      <c r="AE1" s="173" t="s">
+      <c r="AE1" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="AF1" s="173"/>
-      <c r="AG1" s="173"/>
-      <c r="AH1" s="173"/>
-      <c r="AI1" s="173"/>
-      <c r="AJ1" s="173"/>
-      <c r="AK1" s="173"/>
+      <c r="AF1" s="148"/>
+      <c r="AG1" s="148"/>
+      <c r="AH1" s="148"/>
+      <c r="AI1" s="148"/>
+      <c r="AJ1" s="148"/>
+      <c r="AK1" s="148"/>
       <c r="AL1" s="49"/>
-      <c r="AM1" s="172">
+      <c r="AM1" s="149">
         <f>DATE(2026,4,1)</f>
         <v>46113</v>
       </c>
-      <c r="AN1" s="172"/>
-      <c r="AO1" s="172"/>
-      <c r="AP1" s="172"/>
-      <c r="AQ1" s="172"/>
-      <c r="AR1" s="172"/>
-      <c r="AS1" s="172"/>
-      <c r="AT1" s="172"/>
-      <c r="AU1" s="172"/>
-      <c r="AV1" s="172"/>
+      <c r="AN1" s="149"/>
+      <c r="AO1" s="149"/>
+      <c r="AP1" s="149"/>
+      <c r="AQ1" s="149"/>
+      <c r="AR1" s="149"/>
+      <c r="AS1" s="149"/>
+      <c r="AT1" s="149"/>
+      <c r="AU1" s="149"/>
+      <c r="AV1" s="149"/>
     </row>
     <row r="2" spans="1:194" ht="30" customHeight="1">
       <c r="A2" s="47" t="s">
@@ -3191,28 +3191,28 @@
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
-      <c r="K2" s="173" t="s">
+      <c r="K2" s="148" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="173"/>
-      <c r="M2" s="173"/>
-      <c r="N2" s="173"/>
-      <c r="O2" s="173"/>
-      <c r="P2" s="173"/>
-      <c r="Q2" s="173"/>
+      <c r="L2" s="148"/>
+      <c r="M2" s="148"/>
+      <c r="N2" s="148"/>
+      <c r="O2" s="148"/>
+      <c r="P2" s="148"/>
+      <c r="Q2" s="148"/>
       <c r="R2" s="48"/>
-      <c r="S2" s="171">
+      <c r="S2" s="153">
         <v>-1</v>
       </c>
-      <c r="T2" s="171"/>
-      <c r="U2" s="171"/>
-      <c r="V2" s="171"/>
-      <c r="W2" s="171"/>
-      <c r="X2" s="171"/>
-      <c r="Y2" s="171"/>
-      <c r="Z2" s="171"/>
-      <c r="AA2" s="171"/>
-      <c r="AB2" s="171"/>
+      <c r="T2" s="153"/>
+      <c r="U2" s="153"/>
+      <c r="V2" s="153"/>
+      <c r="W2" s="153"/>
+      <c r="X2" s="153"/>
+      <c r="Y2" s="153"/>
+      <c r="Z2" s="153"/>
+      <c r="AA2" s="153"/>
+      <c r="AB2" s="153"/>
       <c r="AC2" s="49"/>
       <c r="AD2" s="49"/>
       <c r="AE2" s="49"/>
@@ -3251,290 +3251,290 @@
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4" s="51"/>
-      <c r="K4" s="175">
+      <c r="K4" s="154">
         <f ca="1">M5</f>
         <v>45971</v>
       </c>
-      <c r="L4" s="175"/>
-      <c r="M4" s="175"/>
-      <c r="N4" s="175"/>
-      <c r="O4" s="175"/>
-      <c r="P4" s="175"/>
-      <c r="Q4" s="175"/>
-      <c r="R4" s="174">
+      <c r="L4" s="154"/>
+      <c r="M4" s="154"/>
+      <c r="N4" s="154"/>
+      <c r="O4" s="154"/>
+      <c r="P4" s="154"/>
+      <c r="Q4" s="154"/>
+      <c r="R4" s="147">
         <f ca="1">T5</f>
         <v>45978</v>
       </c>
-      <c r="S4" s="174"/>
-      <c r="T4" s="174"/>
-      <c r="U4" s="174"/>
-      <c r="V4" s="174"/>
-      <c r="W4" s="174"/>
-      <c r="X4" s="174"/>
-      <c r="Y4" s="174">
+      <c r="S4" s="147"/>
+      <c r="T4" s="147"/>
+      <c r="U4" s="147"/>
+      <c r="V4" s="147"/>
+      <c r="W4" s="147"/>
+      <c r="X4" s="147"/>
+      <c r="Y4" s="147">
         <f ca="1">AA5</f>
         <v>45985</v>
       </c>
-      <c r="Z4" s="174"/>
-      <c r="AA4" s="174"/>
-      <c r="AB4" s="174"/>
-      <c r="AC4" s="174"/>
-      <c r="AD4" s="174"/>
-      <c r="AE4" s="174"/>
-      <c r="AF4" s="174">
+      <c r="Z4" s="147"/>
+      <c r="AA4" s="147"/>
+      <c r="AB4" s="147"/>
+      <c r="AC4" s="147"/>
+      <c r="AD4" s="147"/>
+      <c r="AE4" s="147"/>
+      <c r="AF4" s="147">
         <f ca="1">AH5</f>
         <v>45992</v>
       </c>
-      <c r="AG4" s="174"/>
-      <c r="AH4" s="174"/>
-      <c r="AI4" s="174"/>
-      <c r="AJ4" s="174"/>
-      <c r="AK4" s="174"/>
-      <c r="AL4" s="174"/>
-      <c r="AM4" s="174">
+      <c r="AG4" s="147"/>
+      <c r="AH4" s="147"/>
+      <c r="AI4" s="147"/>
+      <c r="AJ4" s="147"/>
+      <c r="AK4" s="147"/>
+      <c r="AL4" s="147"/>
+      <c r="AM4" s="147">
         <f ca="1">AO5</f>
         <v>45999</v>
       </c>
-      <c r="AN4" s="174"/>
-      <c r="AO4" s="174"/>
-      <c r="AP4" s="174"/>
-      <c r="AQ4" s="174"/>
-      <c r="AR4" s="174"/>
-      <c r="AS4" s="174"/>
-      <c r="AT4" s="174">
+      <c r="AN4" s="147"/>
+      <c r="AO4" s="147"/>
+      <c r="AP4" s="147"/>
+      <c r="AQ4" s="147"/>
+      <c r="AR4" s="147"/>
+      <c r="AS4" s="147"/>
+      <c r="AT4" s="147">
         <f ca="1">AV5</f>
         <v>46006</v>
       </c>
-      <c r="AU4" s="174"/>
-      <c r="AV4" s="174"/>
-      <c r="AW4" s="174"/>
-      <c r="AX4" s="174"/>
-      <c r="AY4" s="174"/>
-      <c r="AZ4" s="174"/>
-      <c r="BA4" s="174">
+      <c r="AU4" s="147"/>
+      <c r="AV4" s="147"/>
+      <c r="AW4" s="147"/>
+      <c r="AX4" s="147"/>
+      <c r="AY4" s="147"/>
+      <c r="AZ4" s="147"/>
+      <c r="BA4" s="147">
         <f ca="1">BC5</f>
         <v>46013</v>
       </c>
-      <c r="BB4" s="174"/>
-      <c r="BC4" s="174"/>
-      <c r="BD4" s="174"/>
-      <c r="BE4" s="174"/>
-      <c r="BF4" s="174"/>
-      <c r="BG4" s="174"/>
-      <c r="BH4" s="174">
+      <c r="BB4" s="147"/>
+      <c r="BC4" s="147"/>
+      <c r="BD4" s="147"/>
+      <c r="BE4" s="147"/>
+      <c r="BF4" s="147"/>
+      <c r="BG4" s="147"/>
+      <c r="BH4" s="147">
         <f ca="1">BJ5</f>
         <v>46020</v>
       </c>
-      <c r="BI4" s="174"/>
-      <c r="BJ4" s="174"/>
-      <c r="BK4" s="174"/>
-      <c r="BL4" s="174"/>
-      <c r="BM4" s="174"/>
-      <c r="BN4" s="174"/>
-      <c r="BO4" s="174">
+      <c r="BI4" s="147"/>
+      <c r="BJ4" s="147"/>
+      <c r="BK4" s="147"/>
+      <c r="BL4" s="147"/>
+      <c r="BM4" s="147"/>
+      <c r="BN4" s="147"/>
+      <c r="BO4" s="147">
         <f ca="1">BQ5</f>
         <v>46027</v>
       </c>
-      <c r="BP4" s="174"/>
-      <c r="BQ4" s="174"/>
-      <c r="BR4" s="174"/>
-      <c r="BS4" s="174"/>
-      <c r="BT4" s="174"/>
-      <c r="BU4" s="174"/>
-      <c r="BV4" s="174">
+      <c r="BP4" s="147"/>
+      <c r="BQ4" s="147"/>
+      <c r="BR4" s="147"/>
+      <c r="BS4" s="147"/>
+      <c r="BT4" s="147"/>
+      <c r="BU4" s="147"/>
+      <c r="BV4" s="147">
         <f ca="1">BX5</f>
         <v>46034</v>
       </c>
-      <c r="BW4" s="174"/>
-      <c r="BX4" s="174"/>
-      <c r="BY4" s="174"/>
-      <c r="BZ4" s="174"/>
-      <c r="CA4" s="174"/>
-      <c r="CB4" s="174"/>
-      <c r="CC4" s="174">
+      <c r="BW4" s="147"/>
+      <c r="BX4" s="147"/>
+      <c r="BY4" s="147"/>
+      <c r="BZ4" s="147"/>
+      <c r="CA4" s="147"/>
+      <c r="CB4" s="147"/>
+      <c r="CC4" s="147">
         <f ca="1">CE5</f>
         <v>46041</v>
       </c>
-      <c r="CD4" s="174"/>
-      <c r="CE4" s="174"/>
-      <c r="CF4" s="174"/>
-      <c r="CG4" s="174"/>
-      <c r="CH4" s="174"/>
-      <c r="CI4" s="174"/>
-      <c r="CJ4" s="174">
+      <c r="CD4" s="147"/>
+      <c r="CE4" s="147"/>
+      <c r="CF4" s="147"/>
+      <c r="CG4" s="147"/>
+      <c r="CH4" s="147"/>
+      <c r="CI4" s="147"/>
+      <c r="CJ4" s="147">
         <f ca="1">CL5</f>
         <v>46048</v>
       </c>
-      <c r="CK4" s="174"/>
-      <c r="CL4" s="174"/>
-      <c r="CM4" s="174"/>
-      <c r="CN4" s="174"/>
-      <c r="CO4" s="174"/>
-      <c r="CP4" s="174"/>
-      <c r="CQ4" s="174">
+      <c r="CK4" s="147"/>
+      <c r="CL4" s="147"/>
+      <c r="CM4" s="147"/>
+      <c r="CN4" s="147"/>
+      <c r="CO4" s="147"/>
+      <c r="CP4" s="147"/>
+      <c r="CQ4" s="147">
         <f ca="1">CS5</f>
         <v>46055</v>
       </c>
-      <c r="CR4" s="174"/>
-      <c r="CS4" s="174"/>
-      <c r="CT4" s="174"/>
-      <c r="CU4" s="174"/>
-      <c r="CV4" s="174"/>
-      <c r="CW4" s="174"/>
-      <c r="CX4" s="174">
+      <c r="CR4" s="147"/>
+      <c r="CS4" s="147"/>
+      <c r="CT4" s="147"/>
+      <c r="CU4" s="147"/>
+      <c r="CV4" s="147"/>
+      <c r="CW4" s="147"/>
+      <c r="CX4" s="147">
         <f ca="1">CZ5</f>
         <v>46062</v>
       </c>
-      <c r="CY4" s="174"/>
-      <c r="CZ4" s="174"/>
-      <c r="DA4" s="174"/>
-      <c r="DB4" s="174"/>
-      <c r="DC4" s="174"/>
-      <c r="DD4" s="174"/>
-      <c r="DE4" s="174">
+      <c r="CY4" s="147"/>
+      <c r="CZ4" s="147"/>
+      <c r="DA4" s="147"/>
+      <c r="DB4" s="147"/>
+      <c r="DC4" s="147"/>
+      <c r="DD4" s="147"/>
+      <c r="DE4" s="147">
         <f ca="1">DG5</f>
         <v>46069</v>
       </c>
-      <c r="DF4" s="174"/>
-      <c r="DG4" s="174"/>
-      <c r="DH4" s="174"/>
-      <c r="DI4" s="174"/>
-      <c r="DJ4" s="174"/>
-      <c r="DK4" s="174"/>
-      <c r="DL4" s="174">
+      <c r="DF4" s="147"/>
+      <c r="DG4" s="147"/>
+      <c r="DH4" s="147"/>
+      <c r="DI4" s="147"/>
+      <c r="DJ4" s="147"/>
+      <c r="DK4" s="147"/>
+      <c r="DL4" s="147">
         <f ca="1">DN5</f>
         <v>46076</v>
       </c>
-      <c r="DM4" s="174"/>
-      <c r="DN4" s="174"/>
-      <c r="DO4" s="174"/>
-      <c r="DP4" s="174"/>
-      <c r="DQ4" s="174"/>
-      <c r="DR4" s="174"/>
-      <c r="DS4" s="174">
+      <c r="DM4" s="147"/>
+      <c r="DN4" s="147"/>
+      <c r="DO4" s="147"/>
+      <c r="DP4" s="147"/>
+      <c r="DQ4" s="147"/>
+      <c r="DR4" s="147"/>
+      <c r="DS4" s="147">
         <f ca="1">DU5</f>
         <v>46083</v>
       </c>
-      <c r="DT4" s="174"/>
-      <c r="DU4" s="174"/>
-      <c r="DV4" s="174"/>
-      <c r="DW4" s="174"/>
-      <c r="DX4" s="174"/>
-      <c r="DY4" s="174"/>
-      <c r="DZ4" s="174">
+      <c r="DT4" s="147"/>
+      <c r="DU4" s="147"/>
+      <c r="DV4" s="147"/>
+      <c r="DW4" s="147"/>
+      <c r="DX4" s="147"/>
+      <c r="DY4" s="147"/>
+      <c r="DZ4" s="147">
         <f ca="1">EB5</f>
         <v>46090</v>
       </c>
-      <c r="EA4" s="174"/>
-      <c r="EB4" s="174"/>
-      <c r="EC4" s="174"/>
-      <c r="ED4" s="174"/>
-      <c r="EE4" s="174"/>
-      <c r="EF4" s="174"/>
-      <c r="EG4" s="174">
+      <c r="EA4" s="147"/>
+      <c r="EB4" s="147"/>
+      <c r="EC4" s="147"/>
+      <c r="ED4" s="147"/>
+      <c r="EE4" s="147"/>
+      <c r="EF4" s="147"/>
+      <c r="EG4" s="147">
         <f ca="1">EI5</f>
         <v>46097</v>
       </c>
-      <c r="EH4" s="174"/>
-      <c r="EI4" s="174"/>
-      <c r="EJ4" s="174"/>
-      <c r="EK4" s="174"/>
-      <c r="EL4" s="174"/>
-      <c r="EM4" s="174"/>
-      <c r="EN4" s="174">
+      <c r="EH4" s="147"/>
+      <c r="EI4" s="147"/>
+      <c r="EJ4" s="147"/>
+      <c r="EK4" s="147"/>
+      <c r="EL4" s="147"/>
+      <c r="EM4" s="147"/>
+      <c r="EN4" s="147">
         <f ca="1">EP5</f>
         <v>46104</v>
       </c>
-      <c r="EO4" s="174"/>
-      <c r="EP4" s="174"/>
-      <c r="EQ4" s="174"/>
-      <c r="ER4" s="174"/>
-      <c r="ES4" s="174"/>
-      <c r="ET4" s="174"/>
-      <c r="EU4" s="174">
+      <c r="EO4" s="147"/>
+      <c r="EP4" s="147"/>
+      <c r="EQ4" s="147"/>
+      <c r="ER4" s="147"/>
+      <c r="ES4" s="147"/>
+      <c r="ET4" s="147"/>
+      <c r="EU4" s="147">
         <f ca="1">EW5</f>
         <v>46111</v>
       </c>
-      <c r="EV4" s="174"/>
-      <c r="EW4" s="174"/>
-      <c r="EX4" s="174"/>
-      <c r="EY4" s="174"/>
-      <c r="EZ4" s="174"/>
-      <c r="FA4" s="174"/>
-      <c r="FB4" s="174">
+      <c r="EV4" s="147"/>
+      <c r="EW4" s="147"/>
+      <c r="EX4" s="147"/>
+      <c r="EY4" s="147"/>
+      <c r="EZ4" s="147"/>
+      <c r="FA4" s="147"/>
+      <c r="FB4" s="147">
         <f ca="1">FD5</f>
         <v>46118</v>
       </c>
-      <c r="FC4" s="174"/>
-      <c r="FD4" s="174"/>
-      <c r="FE4" s="174"/>
-      <c r="FF4" s="174"/>
-      <c r="FG4" s="174"/>
-      <c r="FH4" s="174"/>
-      <c r="FI4" s="174">
+      <c r="FC4" s="147"/>
+      <c r="FD4" s="147"/>
+      <c r="FE4" s="147"/>
+      <c r="FF4" s="147"/>
+      <c r="FG4" s="147"/>
+      <c r="FH4" s="147"/>
+      <c r="FI4" s="147">
         <f ca="1">FK5</f>
         <v>46125</v>
       </c>
-      <c r="FJ4" s="174"/>
-      <c r="FK4" s="174"/>
-      <c r="FL4" s="174"/>
-      <c r="FM4" s="174"/>
-      <c r="FN4" s="174"/>
-      <c r="FO4" s="174"/>
-      <c r="FP4" s="174">
+      <c r="FJ4" s="147"/>
+      <c r="FK4" s="147"/>
+      <c r="FL4" s="147"/>
+      <c r="FM4" s="147"/>
+      <c r="FN4" s="147"/>
+      <c r="FO4" s="147"/>
+      <c r="FP4" s="147">
         <f ca="1">FR5</f>
         <v>46132</v>
       </c>
-      <c r="FQ4" s="174"/>
-      <c r="FR4" s="174"/>
-      <c r="FS4" s="174"/>
-      <c r="FT4" s="174"/>
-      <c r="FU4" s="174"/>
-      <c r="FV4" s="174"/>
-      <c r="FW4" s="174">
+      <c r="FQ4" s="147"/>
+      <c r="FR4" s="147"/>
+      <c r="FS4" s="147"/>
+      <c r="FT4" s="147"/>
+      <c r="FU4" s="147"/>
+      <c r="FV4" s="147"/>
+      <c r="FW4" s="147">
         <f ca="1">FY5</f>
         <v>46139</v>
       </c>
-      <c r="FX4" s="174"/>
-      <c r="FY4" s="174"/>
-      <c r="FZ4" s="174"/>
-      <c r="GA4" s="174"/>
-      <c r="GB4" s="174"/>
-      <c r="GC4" s="174"/>
-      <c r="GD4" s="174">
+      <c r="FX4" s="147"/>
+      <c r="FY4" s="147"/>
+      <c r="FZ4" s="147"/>
+      <c r="GA4" s="147"/>
+      <c r="GB4" s="147"/>
+      <c r="GC4" s="147"/>
+      <c r="GD4" s="147">
         <f ca="1">GF5</f>
         <v>46146</v>
       </c>
-      <c r="GE4" s="174"/>
-      <c r="GF4" s="174"/>
-      <c r="GG4" s="174"/>
-      <c r="GH4" s="174"/>
-      <c r="GI4" s="174"/>
-      <c r="GJ4" s="174"/>
+      <c r="GE4" s="147"/>
+      <c r="GF4" s="147"/>
+      <c r="GG4" s="147"/>
+      <c r="GH4" s="147"/>
+      <c r="GI4" s="147"/>
+      <c r="GJ4" s="147"/>
     </row>
     <row r="5" spans="1:194" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="176" t="s">
+      <c r="A5" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="176" t="s">
+      <c r="B5" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="177" t="s">
+      <c r="C5" s="151" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="178" t="s">
+      <c r="D5" s="152" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="178" t="s">
+      <c r="E5" s="152" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="178" t="s">
+      <c r="F5" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="178" t="s">
+      <c r="G5" s="152" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="178" t="s">
+      <c r="H5" s="152" t="s">
         <v>13</v>
       </c>
       <c r="I5" s="50"/>
@@ -4265,14 +4265,14 @@
       <c r="GL5" s="19"/>
     </row>
     <row r="6" spans="1:194" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="176"/>
-      <c r="B6" s="176"/>
-      <c r="C6" s="177"/>
-      <c r="D6" s="178"/>
-      <c r="E6" s="178"/>
-      <c r="F6" s="178"/>
-      <c r="G6" s="178"/>
-      <c r="H6" s="178"/>
+      <c r="A6" s="150"/>
+      <c r="B6" s="150"/>
+      <c r="C6" s="151"/>
+      <c r="D6" s="152"/>
+      <c r="E6" s="152"/>
+      <c r="F6" s="152"/>
+      <c r="G6" s="152"/>
+      <c r="H6" s="152"/>
       <c r="I6" s="38"/>
       <c r="J6" s="39"/>
       <c r="K6" s="36"/>
@@ -5269,10 +5269,10 @@
       <c r="GJ8" s="42"/>
     </row>
     <row r="9" spans="1:194" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A9" s="166" t="s">
+      <c r="A9" s="155" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="154" t="s">
+      <c r="B9" s="167" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="129" t="s">
@@ -5287,7 +5287,7 @@
       <c r="F9" s="118">
         <v>45976</v>
       </c>
-      <c r="G9" s="164" t="s">
+      <c r="G9" s="177" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="102" t="s">
@@ -5481,8 +5481,8 @@
       <c r="GJ9" s="112"/>
     </row>
     <row r="10" spans="1:194" s="114" customFormat="1" ht="87" customHeight="1" thickBot="1">
-      <c r="A10" s="166"/>
-      <c r="B10" s="154"/>
+      <c r="A10" s="155"/>
+      <c r="B10" s="167"/>
       <c r="C10" s="132" t="s">
         <v>16</v>
       </c>
@@ -5495,7 +5495,7 @@
       <c r="F10" s="126">
         <v>45968</v>
       </c>
-      <c r="G10" s="165"/>
+      <c r="G10" s="178"/>
       <c r="H10" s="107" t="s">
         <v>19</v>
       </c>
@@ -5681,8 +5681,8 @@
       <c r="GJ10" s="112"/>
     </row>
     <row r="11" spans="1:194" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A11" s="166"/>
-      <c r="B11" s="154"/>
+      <c r="A11" s="155"/>
+      <c r="B11" s="167"/>
       <c r="C11" s="133" t="s">
         <v>16</v>
       </c>
@@ -5695,7 +5695,7 @@
       <c r="F11" s="125">
         <v>45968</v>
       </c>
-      <c r="G11" s="165"/>
+      <c r="G11" s="178"/>
       <c r="H11" s="102" t="s">
         <v>20</v>
       </c>
@@ -5886,8 +5886,8 @@
       <c r="GJ11" s="34"/>
     </row>
     <row r="12" spans="1:194" s="28" customFormat="1" ht="53.25" thickBot="1">
-      <c r="A12" s="166"/>
-      <c r="B12" s="155"/>
+      <c r="A12" s="155"/>
+      <c r="B12" s="168"/>
       <c r="C12" s="104" t="s">
         <v>16</v>
       </c>
@@ -6095,10 +6095,10 @@
       <c r="GJ12" s="34"/>
     </row>
     <row r="13" spans="1:194" s="28" customFormat="1" ht="106.15" thickBot="1">
-      <c r="A13" s="167" t="s">
+      <c r="A13" s="156" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="156" t="s">
+      <c r="B13" s="169" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="87" t="s">
@@ -6302,15 +6302,15 @@
       <c r="GJ13" s="34"/>
     </row>
     <row r="14" spans="1:194" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A14" s="167"/>
-      <c r="B14" s="156"/>
+      <c r="A14" s="156"/>
+      <c r="B14" s="169"/>
       <c r="C14" s="121" t="s">
         <v>28</v>
       </c>
       <c r="D14" s="88"/>
       <c r="E14" s="89"/>
       <c r="F14" s="89"/>
-      <c r="G14" s="158" t="s">
+      <c r="G14" s="171" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="119" t="s">
@@ -6502,15 +6502,15 @@
       <c r="GJ14" s="29"/>
     </row>
     <row r="15" spans="1:194" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A15" s="167"/>
-      <c r="B15" s="156"/>
+      <c r="A15" s="156"/>
+      <c r="B15" s="169"/>
       <c r="C15" s="120" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="88"/>
       <c r="E15" s="89"/>
       <c r="F15" s="89"/>
-      <c r="G15" s="159"/>
+      <c r="G15" s="172"/>
       <c r="H15" s="101" t="s">
         <v>31</v>
       </c>
@@ -6700,15 +6700,15 @@
       <c r="GJ15" s="29"/>
     </row>
     <row r="16" spans="1:194" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A16" s="167"/>
-      <c r="B16" s="156"/>
+      <c r="A16" s="156"/>
+      <c r="B16" s="169"/>
       <c r="C16" s="87" t="s">
         <v>32</v>
       </c>
       <c r="D16" s="88"/>
       <c r="E16" s="90"/>
       <c r="F16" s="91"/>
-      <c r="G16" s="160"/>
+      <c r="G16" s="173"/>
       <c r="H16" s="101" t="s">
         <v>33</v>
       </c>
@@ -6901,8 +6901,8 @@
       <c r="GJ16" s="141"/>
     </row>
     <row r="17" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A17" s="167"/>
-      <c r="B17" s="156"/>
+      <c r="A17" s="156"/>
+      <c r="B17" s="169"/>
       <c r="C17" s="87" t="s">
         <v>34</v>
       </c>
@@ -7104,8 +7104,8 @@
       <c r="GJ17" s="34"/>
     </row>
     <row r="18" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A18" s="167"/>
-      <c r="B18" s="156"/>
+      <c r="A18" s="156"/>
+      <c r="B18" s="169"/>
       <c r="C18" s="87" t="s">
         <v>34</v>
       </c>
@@ -7307,10 +7307,10 @@
       <c r="GJ18" s="34"/>
     </row>
     <row r="19" spans="1:193" s="28" customFormat="1" ht="88.5" thickBot="1">
-      <c r="A19" s="168" t="s">
+      <c r="A19" s="157" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="153" t="s">
+      <c r="B19" s="166" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="78" t="s">
@@ -7319,7 +7319,7 @@
       <c r="D19" s="79"/>
       <c r="E19" s="80"/>
       <c r="F19" s="80"/>
-      <c r="G19" s="161" t="s">
+      <c r="G19" s="174" t="s">
         <v>42</v>
       </c>
       <c r="H19" s="122" t="s">
@@ -7514,15 +7514,15 @@
       <c r="GJ19" s="34"/>
     </row>
     <row r="20" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A20" s="168"/>
-      <c r="B20" s="153"/>
+      <c r="A20" s="157"/>
+      <c r="B20" s="166"/>
       <c r="C20" s="78" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="79"/>
       <c r="E20" s="80"/>
       <c r="F20" s="80"/>
-      <c r="G20" s="162"/>
+      <c r="G20" s="175"/>
       <c r="H20" s="122" t="s">
         <v>45</v>
       </c>
@@ -7715,15 +7715,15 @@
       <c r="GJ20" s="34"/>
     </row>
     <row r="21" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A21" s="168"/>
-      <c r="B21" s="153"/>
+      <c r="A21" s="157"/>
+      <c r="B21" s="166"/>
       <c r="C21" s="78" t="s">
         <v>44</v>
       </c>
       <c r="D21" s="79"/>
       <c r="E21" s="80"/>
       <c r="F21" s="80"/>
-      <c r="G21" s="162"/>
+      <c r="G21" s="175"/>
       <c r="H21" s="122" t="s">
         <v>46</v>
       </c>
@@ -7916,15 +7916,15 @@
       <c r="GJ21" s="34"/>
     </row>
     <row r="22" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A22" s="168"/>
-      <c r="B22" s="153"/>
+      <c r="A22" s="157"/>
+      <c r="B22" s="166"/>
       <c r="C22" s="78" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="79"/>
       <c r="E22" s="81"/>
       <c r="F22" s="82"/>
-      <c r="G22" s="163"/>
+      <c r="G22" s="176"/>
       <c r="H22" s="99" t="s">
         <v>47</v>
       </c>
@@ -8117,15 +8117,15 @@
       <c r="GJ22" s="34"/>
     </row>
     <row r="23" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A23" s="168"/>
-      <c r="B23" s="153"/>
+      <c r="A23" s="157"/>
+      <c r="B23" s="166"/>
       <c r="C23" s="78" t="s">
         <v>44</v>
       </c>
       <c r="D23" s="79"/>
       <c r="E23" s="80"/>
       <c r="F23" s="80"/>
-      <c r="G23" s="162" t="s">
+      <c r="G23" s="175" t="s">
         <v>48</v>
       </c>
       <c r="H23" s="123" t="s">
@@ -8320,15 +8320,15 @@
       <c r="GJ23" s="34"/>
     </row>
     <row r="24" spans="1:193" s="28" customFormat="1" ht="52.5" thickBot="1">
-      <c r="A24" s="168"/>
-      <c r="B24" s="153"/>
+      <c r="A24" s="157"/>
+      <c r="B24" s="166"/>
       <c r="C24" s="78" t="s">
         <v>44</v>
       </c>
       <c r="D24" s="79"/>
       <c r="E24" s="80"/>
       <c r="F24" s="80"/>
-      <c r="G24" s="162"/>
+      <c r="G24" s="175"/>
       <c r="H24" s="122" t="s">
         <v>50</v>
       </c>
@@ -8521,15 +8521,15 @@
       <c r="GJ24" s="34"/>
     </row>
     <row r="25" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A25" s="168"/>
-      <c r="B25" s="153"/>
+      <c r="A25" s="157"/>
+      <c r="B25" s="166"/>
       <c r="C25" s="78" t="s">
         <v>51</v>
       </c>
       <c r="D25" s="79"/>
       <c r="E25" s="80"/>
       <c r="F25" s="80"/>
-      <c r="G25" s="163"/>
+      <c r="G25" s="176"/>
       <c r="H25" s="134" t="s">
         <v>52</v>
       </c>
@@ -8722,10 +8722,10 @@
       <c r="GJ25" s="34"/>
     </row>
     <row r="26" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A26" s="169" t="s">
+      <c r="A26" s="158" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="157" t="s">
+      <c r="B26" s="170" t="s">
         <v>54</v>
       </c>
       <c r="C26" s="92" t="s">
@@ -8734,7 +8734,7 @@
       <c r="D26" s="93"/>
       <c r="E26" s="94"/>
       <c r="F26" s="94"/>
-      <c r="G26" s="150" t="s">
+      <c r="G26" s="163" t="s">
         <v>56</v>
       </c>
       <c r="H26" s="140" t="s">
@@ -8929,15 +8929,15 @@
       <c r="GJ26" s="34"/>
     </row>
     <row r="27" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A27" s="169"/>
-      <c r="B27" s="157"/>
+      <c r="A27" s="158"/>
+      <c r="B27" s="170"/>
       <c r="C27" s="92" t="s">
         <v>51</v>
       </c>
       <c r="D27" s="93"/>
       <c r="E27" s="94"/>
       <c r="F27" s="94"/>
-      <c r="G27" s="151"/>
+      <c r="G27" s="164"/>
       <c r="H27" s="135" t="s">
         <v>58</v>
       </c>
@@ -9130,15 +9130,15 @@
       <c r="GJ27" s="34"/>
     </row>
     <row r="28" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A28" s="169"/>
-      <c r="B28" s="157"/>
+      <c r="A28" s="158"/>
+      <c r="B28" s="170"/>
       <c r="C28" s="92" t="s">
         <v>51</v>
       </c>
       <c r="D28" s="93"/>
       <c r="E28" s="95"/>
       <c r="F28" s="96"/>
-      <c r="G28" s="152"/>
+      <c r="G28" s="165"/>
       <c r="H28" s="135" t="s">
         <v>59</v>
       </c>
@@ -9332,8 +9332,8 @@
       <c r="GK28" s="141"/>
     </row>
     <row r="29" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A29" s="169"/>
-      <c r="B29" s="157"/>
+      <c r="A29" s="158"/>
+      <c r="B29" s="170"/>
       <c r="C29" s="92" t="s">
         <v>55</v>
       </c>
@@ -9536,8 +9536,8 @@
       <c r="GK29" s="141"/>
     </row>
     <row r="30" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A30" s="169"/>
-      <c r="B30" s="157"/>
+      <c r="A30" s="158"/>
+      <c r="B30" s="170"/>
       <c r="C30" s="92" t="s">
         <v>41</v>
       </c>
@@ -9740,10 +9740,10 @@
       <c r="GK30" s="141"/>
     </row>
     <row r="31" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A31" s="170" t="s">
+      <c r="A31" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="147" t="s">
+      <c r="B31" s="160" t="s">
         <v>64</v>
       </c>
       <c r="C31" s="83" t="s">
@@ -9948,8 +9948,8 @@
       <c r="GK31" s="141"/>
     </row>
     <row r="32" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A32" s="170"/>
-      <c r="B32" s="148"/>
+      <c r="A32" s="159"/>
+      <c r="B32" s="161"/>
       <c r="C32" s="83" t="s">
         <v>41</v>
       </c>
@@ -10152,8 +10152,8 @@
       <c r="GK32" s="141"/>
     </row>
     <row r="33" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A33" s="170"/>
-      <c r="B33" s="148"/>
+      <c r="A33" s="159"/>
+      <c r="B33" s="161"/>
       <c r="C33" s="83" t="s">
         <v>41</v>
       </c>
@@ -10356,8 +10356,8 @@
       <c r="GK33" s="141"/>
     </row>
     <row r="34" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A34" s="170"/>
-      <c r="B34" s="148"/>
+      <c r="A34" s="159"/>
+      <c r="B34" s="161"/>
       <c r="C34" s="83" t="s">
         <v>41</v>
       </c>
@@ -10560,8 +10560,8 @@
       <c r="GK34" s="141"/>
     </row>
     <row r="35" spans="1:193" s="28" customFormat="1" ht="106.15" thickBot="1">
-      <c r="A35" s="170"/>
-      <c r="B35" s="148"/>
+      <c r="A35" s="159"/>
+      <c r="B35" s="161"/>
       <c r="C35" s="137" t="s">
         <v>41</v>
       </c>
@@ -10764,8 +10764,8 @@
       <c r="GK35" s="141"/>
     </row>
     <row r="36" spans="1:193" ht="88.15" customHeight="1">
-      <c r="A36" s="170"/>
-      <c r="B36" s="149"/>
+      <c r="A36" s="159"/>
+      <c r="B36" s="162"/>
       <c r="C36" s="138" t="s">
         <v>41</v>
       </c>
@@ -11121,6 +11121,45 @@
   </sheetData>
   <autoFilter ref="A8:H36" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="55">
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="B19:B25"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="S2:AB2"/>
+    <mergeCell ref="S1:AB1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="BH4:BN4"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="Y4:AE4"/>
+    <mergeCell ref="AF4:AL4"/>
+    <mergeCell ref="AM4:AS4"/>
+    <mergeCell ref="AT4:AZ4"/>
+    <mergeCell ref="BA4:BG4"/>
+    <mergeCell ref="BV4:CB4"/>
+    <mergeCell ref="CC4:CI4"/>
+    <mergeCell ref="CJ4:CP4"/>
+    <mergeCell ref="CQ4:CW4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
     <mergeCell ref="FP4:FV4"/>
     <mergeCell ref="FW4:GC4"/>
     <mergeCell ref="GD4:GJ4"/>
@@ -11137,45 +11176,6 @@
     <mergeCell ref="DS4:DY4"/>
     <mergeCell ref="DZ4:EF4"/>
     <mergeCell ref="BO4:BU4"/>
-    <mergeCell ref="BV4:CB4"/>
-    <mergeCell ref="CC4:CI4"/>
-    <mergeCell ref="CJ4:CP4"/>
-    <mergeCell ref="CQ4:CW4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="S2:AB2"/>
-    <mergeCell ref="S1:AB1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="BH4:BN4"/>
-    <mergeCell ref="K4:Q4"/>
-    <mergeCell ref="R4:X4"/>
-    <mergeCell ref="Y4:AE4"/>
-    <mergeCell ref="AF4:AL4"/>
-    <mergeCell ref="AM4:AS4"/>
-    <mergeCell ref="AT4:AZ4"/>
-    <mergeCell ref="BA4:BG4"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="A26:A30"/>
-    <mergeCell ref="A31:A36"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="B19:B25"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="G19:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G9:G11"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D35">
     <cfRule type="dataBar" priority="316">
@@ -11432,7 +11432,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="27">
+    <row r="3" spans="1:6" ht="28.5">
       <c r="A3" s="142" t="s">
         <v>26</v>
       </c>
@@ -11466,7 +11466,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="27">
+    <row r="5" spans="1:6" ht="28.5">
       <c r="A5" s="142" t="s">
         <v>92</v>
       </c>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="C9" s="145"/>
     </row>
-    <row r="10" spans="1:3" ht="27">
+    <row r="10" spans="1:3" ht="28.5">
       <c r="A10" t="s">
         <v>154</v>
       </c>
@@ -12058,35 +12058,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12398,8 +12369,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12407,7 +12407,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/documentation/Systems Develpoment GANTT CHART.xlsx
+++ b/documentation/Systems Develpoment GANTT CHART.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29518"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29629"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uweacuk-my.sharepoint.com/personal/hasaan2_ahmad_live_uwe_ac_uk/Documents/BSc Computer Science/BSC CS YEAR 2/Systems Development - Group Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uweacuk-my.sharepoint.com/personal/hasaan2_ahmad_live_uwe_ac_uk/Documents/BSc Computer Science/BSC CS YEAR 2/Systems Development - Group Project/UFCF7S-30-2---Systems-Development-Group-Project/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1126" documentId="11_3C4179B01545E19DD6C385890107473B0B440F85" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28ABD61D-D402-48E1-8A1E-A069C71E3300}"/>
+  <xr:revisionPtr revIDLastSave="1140" documentId="11_3C4179B01545E19DD6C385890107473B0B440F85" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0181B7B3-AC90-4438-B539-817B7EA2A0F5}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project schedule" sheetId="11" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="228">
   <si>
     <t>SD (Systems Development) Group Project</t>
   </si>
@@ -65,7 +65,7 @@
     <t>Display week:</t>
   </si>
   <si>
-    <t xml:space="preserve">Hasaan (Project Manager), Rayyan (Technical Lead),  Royden (UI/UX Lead), Ishaq (Data Engineer) </t>
+    <t>Hasaan (Project Manager), Rayyan (Technical Lead),  Royden (UI/UX Design), Ishaq (Data Engineer) , Chouaib (UI/UX Design)</t>
   </si>
   <si>
     <t>OBJECTIVE</t>
@@ -122,7 +122,7 @@
     <t>Objective 2: Historical Data Visualization</t>
   </si>
   <si>
-    <t>Design and implement interactive dashboard displaying historical sales trends for top 6 products</t>
+    <t>Design and implement interactive dashboard displaying historical sales trends for top products</t>
   </si>
   <si>
     <t>Rayyan</t>
@@ -131,16 +131,13 @@
     <t>FR2</t>
   </si>
   <si>
-    <t>Dashboard displaying historical sales trends for the top 3 food items and top 3 coffee products</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Royden </t>
+    <t>Dashboard displaying historical sales trends for the top food items and top 1 (of 2) coffee products</t>
   </si>
   <si>
     <t>FR3</t>
   </si>
   <si>
-    <t>Dashboard displays 6 distinct charts showing 4+ weeks of sales data with clear axes</t>
+    <t>Dashboard displays distinct charts showing 4+ weeks of sales data with clear axes</t>
   </si>
   <si>
     <t>Implement product ranking logic (FR2)</t>
@@ -159,6 +156,9 @@
   </si>
   <si>
     <t>Apply Bristol-Pink color scheme</t>
+  </si>
+  <si>
+    <t>Royden, Rayyan, Chouaib</t>
   </si>
   <si>
     <t>NFR3 &amp; NFR5</t>
@@ -218,7 +218,7 @@
     <t>Implement user-interactive features for training period selection, zoom, and predictions vs actuals</t>
   </si>
   <si>
-    <t>Ishaq, Rayyan</t>
+    <t>Chouaib</t>
   </si>
   <si>
     <t>FR4 -  Sales Predictions</t>
@@ -233,6 +233,9 @@
     <t>Implement comparison view - overlay charts</t>
   </si>
   <si>
+    <t>Chouaib, Ishaq</t>
+  </si>
+  <si>
     <t>FR4 -  Sales Predictions &amp;  NFR7 - Security</t>
   </si>
   <si>
@@ -311,7 +314,7 @@
     <t>Must</t>
   </si>
   <si>
-    <t>Display Top 3 Products</t>
+    <t>Display Top Products</t>
   </si>
   <si>
     <t>System must show most-sold Croissant (1 class) &amp; Coffee (2 classes) in chart, auto-updating for last 4 weeks, by Week 5.</t>
@@ -323,7 +326,7 @@
     <t>Sales Fluctuation Graph</t>
   </si>
   <si>
-    <t>System provides selectable line graph of sales fluctuation for 6 items; user can set 4-week window by end of Week 6.</t>
+    <t>System provides selectable line graph of sales fluctuation for each item; user can set 4-week window by end of Week 6.</t>
   </si>
   <si>
     <t>Graph updates when user changes date window; matches data.</t>
@@ -2120,14 +2123,92 @@
     <xf numFmtId="0" fontId="25" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="166" fontId="12" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -2137,84 +2218,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2232,7 +2235,19 @@
     <cellStyle name="Title" xfId="5" builtinId="15" customBuiltin="1"/>
     <cellStyle name="zHiddenText" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
-  <dxfs count="43">
+  <dxfs count="41">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2246,6 +2261,120 @@
         <bottom style="thin">
           <color theme="0" tint="-4.9989318521683403E-2"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2283,6 +2412,86 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="4" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -2304,6 +2513,40 @@
         </patternFill>
       </fill>
       <border>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
         <top style="thin">
           <color theme="0" tint="-4.9989318521683403E-2"/>
         </top>
@@ -2403,244 +2646,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="5"/>
-        </left>
-        <right style="thin">
-          <color theme="5"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="5"/>
-        </left>
-        <right style="thin">
-          <color theme="5"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="5"/>
-        </left>
-        <right style="thin">
-          <color theme="5"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="5"/>
-        </left>
-        <right style="thin">
-          <color theme="5"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="5"/>
-        </left>
-        <right style="thin">
-          <color theme="5"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="8"/>
         </patternFill>
       </fill>
@@ -2663,34 +2668,10 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
       <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
         <top style="thin">
           <color theme="0" tint="-4.9989318521683403E-2"/>
         </top>
@@ -2795,15 +2776,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="ToDoList" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="42"/>
-      <tableStyleElement type="headerRow" dxfId="41"/>
-      <tableStyleElement type="totalRow" dxfId="40"/>
-      <tableStyleElement type="firstColumn" dxfId="39"/>
-      <tableStyleElement type="lastColumn" dxfId="38"/>
-      <tableStyleElement type="firstRowStripe" dxfId="37"/>
-      <tableStyleElement type="secondRowStripe" dxfId="36"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="35"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="34"/>
+      <tableStyleElement type="wholeTable" dxfId="40"/>
+      <tableStyleElement type="headerRow" dxfId="39"/>
+      <tableStyleElement type="totalRow" dxfId="38"/>
+      <tableStyleElement type="firstColumn" dxfId="37"/>
+      <tableStyleElement type="lastColumn" dxfId="36"/>
+      <tableStyleElement type="firstRowStripe" dxfId="35"/>
+      <tableStyleElement type="secondRowStripe" dxfId="34"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="33"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="32"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3131,54 +3112,54 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="J1" s="1"/>
-      <c r="K1" s="148" t="s">
+      <c r="K1" s="173" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="148"/>
-      <c r="O1" s="148"/>
-      <c r="P1" s="148"/>
-      <c r="Q1" s="148"/>
+      <c r="L1" s="173"/>
+      <c r="M1" s="173"/>
+      <c r="N1" s="173"/>
+      <c r="O1" s="173"/>
+      <c r="P1" s="173"/>
+      <c r="Q1" s="173"/>
       <c r="R1" s="48"/>
-      <c r="S1" s="149">
+      <c r="S1" s="172">
         <f ca="1">TODAY()</f>
-        <v>45984</v>
-      </c>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
-      <c r="V1" s="149"/>
-      <c r="W1" s="149"/>
-      <c r="X1" s="149"/>
-      <c r="Y1" s="149"/>
-      <c r="Z1" s="149"/>
-      <c r="AA1" s="149"/>
-      <c r="AB1" s="149"/>
+        <v>46024</v>
+      </c>
+      <c r="T1" s="172"/>
+      <c r="U1" s="172"/>
+      <c r="V1" s="172"/>
+      <c r="W1" s="172"/>
+      <c r="X1" s="172"/>
+      <c r="Y1" s="172"/>
+      <c r="Z1" s="172"/>
+      <c r="AA1" s="172"/>
+      <c r="AB1" s="172"/>
       <c r="AC1" s="49"/>
       <c r="AD1" s="49"/>
-      <c r="AE1" s="148" t="s">
+      <c r="AE1" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="AF1" s="148"/>
-      <c r="AG1" s="148"/>
-      <c r="AH1" s="148"/>
-      <c r="AI1" s="148"/>
-      <c r="AJ1" s="148"/>
-      <c r="AK1" s="148"/>
+      <c r="AF1" s="173"/>
+      <c r="AG1" s="173"/>
+      <c r="AH1" s="173"/>
+      <c r="AI1" s="173"/>
+      <c r="AJ1" s="173"/>
+      <c r="AK1" s="173"/>
       <c r="AL1" s="49"/>
-      <c r="AM1" s="149">
+      <c r="AM1" s="172">
         <f>DATE(2026,4,1)</f>
         <v>46113</v>
       </c>
-      <c r="AN1" s="149"/>
-      <c r="AO1" s="149"/>
-      <c r="AP1" s="149"/>
-      <c r="AQ1" s="149"/>
-      <c r="AR1" s="149"/>
-      <c r="AS1" s="149"/>
-      <c r="AT1" s="149"/>
-      <c r="AU1" s="149"/>
-      <c r="AV1" s="149"/>
+      <c r="AN1" s="172"/>
+      <c r="AO1" s="172"/>
+      <c r="AP1" s="172"/>
+      <c r="AQ1" s="172"/>
+      <c r="AR1" s="172"/>
+      <c r="AS1" s="172"/>
+      <c r="AT1" s="172"/>
+      <c r="AU1" s="172"/>
+      <c r="AV1" s="172"/>
     </row>
     <row r="2" spans="1:194" ht="30" customHeight="1">
       <c r="A2" s="47" t="s">
@@ -3191,28 +3172,28 @@
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
-      <c r="K2" s="148" t="s">
+      <c r="K2" s="173" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="148"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="148"/>
-      <c r="O2" s="148"/>
-      <c r="P2" s="148"/>
-      <c r="Q2" s="148"/>
+      <c r="L2" s="173"/>
+      <c r="M2" s="173"/>
+      <c r="N2" s="173"/>
+      <c r="O2" s="173"/>
+      <c r="P2" s="173"/>
+      <c r="Q2" s="173"/>
       <c r="R2" s="48"/>
-      <c r="S2" s="153">
+      <c r="S2" s="171">
         <v>-1</v>
       </c>
-      <c r="T2" s="153"/>
-      <c r="U2" s="153"/>
-      <c r="V2" s="153"/>
-      <c r="W2" s="153"/>
-      <c r="X2" s="153"/>
-      <c r="Y2" s="153"/>
-      <c r="Z2" s="153"/>
-      <c r="AA2" s="153"/>
-      <c r="AB2" s="153"/>
+      <c r="T2" s="171"/>
+      <c r="U2" s="171"/>
+      <c r="V2" s="171"/>
+      <c r="W2" s="171"/>
+      <c r="X2" s="171"/>
+      <c r="Y2" s="171"/>
+      <c r="Z2" s="171"/>
+      <c r="AA2" s="171"/>
+      <c r="AB2" s="171"/>
       <c r="AC2" s="49"/>
       <c r="AD2" s="49"/>
       <c r="AE2" s="49"/>
@@ -3251,290 +3232,290 @@
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4" s="51"/>
-      <c r="K4" s="154">
+      <c r="K4" s="175">
         <f ca="1">M5</f>
-        <v>45971</v>
-      </c>
-      <c r="L4" s="154"/>
-      <c r="M4" s="154"/>
-      <c r="N4" s="154"/>
-      <c r="O4" s="154"/>
-      <c r="P4" s="154"/>
-      <c r="Q4" s="154"/>
-      <c r="R4" s="147">
+        <v>46006</v>
+      </c>
+      <c r="L4" s="175"/>
+      <c r="M4" s="175"/>
+      <c r="N4" s="175"/>
+      <c r="O4" s="175"/>
+      <c r="P4" s="175"/>
+      <c r="Q4" s="175"/>
+      <c r="R4" s="174">
         <f ca="1">T5</f>
-        <v>45978</v>
-      </c>
-      <c r="S4" s="147"/>
-      <c r="T4" s="147"/>
-      <c r="U4" s="147"/>
-      <c r="V4" s="147"/>
-      <c r="W4" s="147"/>
-      <c r="X4" s="147"/>
-      <c r="Y4" s="147">
+        <v>46013</v>
+      </c>
+      <c r="S4" s="174"/>
+      <c r="T4" s="174"/>
+      <c r="U4" s="174"/>
+      <c r="V4" s="174"/>
+      <c r="W4" s="174"/>
+      <c r="X4" s="174"/>
+      <c r="Y4" s="174">
         <f ca="1">AA5</f>
-        <v>45985</v>
-      </c>
-      <c r="Z4" s="147"/>
-      <c r="AA4" s="147"/>
-      <c r="AB4" s="147"/>
-      <c r="AC4" s="147"/>
-      <c r="AD4" s="147"/>
-      <c r="AE4" s="147"/>
-      <c r="AF4" s="147">
+        <v>46020</v>
+      </c>
+      <c r="Z4" s="174"/>
+      <c r="AA4" s="174"/>
+      <c r="AB4" s="174"/>
+      <c r="AC4" s="174"/>
+      <c r="AD4" s="174"/>
+      <c r="AE4" s="174"/>
+      <c r="AF4" s="174">
         <f ca="1">AH5</f>
-        <v>45992</v>
-      </c>
-      <c r="AG4" s="147"/>
-      <c r="AH4" s="147"/>
-      <c r="AI4" s="147"/>
-      <c r="AJ4" s="147"/>
-      <c r="AK4" s="147"/>
-      <c r="AL4" s="147"/>
-      <c r="AM4" s="147">
+        <v>46027</v>
+      </c>
+      <c r="AG4" s="174"/>
+      <c r="AH4" s="174"/>
+      <c r="AI4" s="174"/>
+      <c r="AJ4" s="174"/>
+      <c r="AK4" s="174"/>
+      <c r="AL4" s="174"/>
+      <c r="AM4" s="174">
         <f ca="1">AO5</f>
-        <v>45999</v>
-      </c>
-      <c r="AN4" s="147"/>
-      <c r="AO4" s="147"/>
-      <c r="AP4" s="147"/>
-      <c r="AQ4" s="147"/>
-      <c r="AR4" s="147"/>
-      <c r="AS4" s="147"/>
-      <c r="AT4" s="147">
+        <v>46034</v>
+      </c>
+      <c r="AN4" s="174"/>
+      <c r="AO4" s="174"/>
+      <c r="AP4" s="174"/>
+      <c r="AQ4" s="174"/>
+      <c r="AR4" s="174"/>
+      <c r="AS4" s="174"/>
+      <c r="AT4" s="174">
         <f ca="1">AV5</f>
-        <v>46006</v>
-      </c>
-      <c r="AU4" s="147"/>
-      <c r="AV4" s="147"/>
-      <c r="AW4" s="147"/>
-      <c r="AX4" s="147"/>
-      <c r="AY4" s="147"/>
-      <c r="AZ4" s="147"/>
-      <c r="BA4" s="147">
+        <v>46041</v>
+      </c>
+      <c r="AU4" s="174"/>
+      <c r="AV4" s="174"/>
+      <c r="AW4" s="174"/>
+      <c r="AX4" s="174"/>
+      <c r="AY4" s="174"/>
+      <c r="AZ4" s="174"/>
+      <c r="BA4" s="174">
         <f ca="1">BC5</f>
-        <v>46013</v>
-      </c>
-      <c r="BB4" s="147"/>
-      <c r="BC4" s="147"/>
-      <c r="BD4" s="147"/>
-      <c r="BE4" s="147"/>
-      <c r="BF4" s="147"/>
-      <c r="BG4" s="147"/>
-      <c r="BH4" s="147">
+        <v>46048</v>
+      </c>
+      <c r="BB4" s="174"/>
+      <c r="BC4" s="174"/>
+      <c r="BD4" s="174"/>
+      <c r="BE4" s="174"/>
+      <c r="BF4" s="174"/>
+      <c r="BG4" s="174"/>
+      <c r="BH4" s="174">
         <f ca="1">BJ5</f>
-        <v>46020</v>
-      </c>
-      <c r="BI4" s="147"/>
-      <c r="BJ4" s="147"/>
-      <c r="BK4" s="147"/>
-      <c r="BL4" s="147"/>
-      <c r="BM4" s="147"/>
-      <c r="BN4" s="147"/>
-      <c r="BO4" s="147">
+        <v>46055</v>
+      </c>
+      <c r="BI4" s="174"/>
+      <c r="BJ4" s="174"/>
+      <c r="BK4" s="174"/>
+      <c r="BL4" s="174"/>
+      <c r="BM4" s="174"/>
+      <c r="BN4" s="174"/>
+      <c r="BO4" s="174">
         <f ca="1">BQ5</f>
-        <v>46027</v>
-      </c>
-      <c r="BP4" s="147"/>
-      <c r="BQ4" s="147"/>
-      <c r="BR4" s="147"/>
-      <c r="BS4" s="147"/>
-      <c r="BT4" s="147"/>
-      <c r="BU4" s="147"/>
-      <c r="BV4" s="147">
+        <v>46062</v>
+      </c>
+      <c r="BP4" s="174"/>
+      <c r="BQ4" s="174"/>
+      <c r="BR4" s="174"/>
+      <c r="BS4" s="174"/>
+      <c r="BT4" s="174"/>
+      <c r="BU4" s="174"/>
+      <c r="BV4" s="174">
         <f ca="1">BX5</f>
-        <v>46034</v>
-      </c>
-      <c r="BW4" s="147"/>
-      <c r="BX4" s="147"/>
-      <c r="BY4" s="147"/>
-      <c r="BZ4" s="147"/>
-      <c r="CA4" s="147"/>
-      <c r="CB4" s="147"/>
-      <c r="CC4" s="147">
+        <v>46069</v>
+      </c>
+      <c r="BW4" s="174"/>
+      <c r="BX4" s="174"/>
+      <c r="BY4" s="174"/>
+      <c r="BZ4" s="174"/>
+      <c r="CA4" s="174"/>
+      <c r="CB4" s="174"/>
+      <c r="CC4" s="174">
         <f ca="1">CE5</f>
-        <v>46041</v>
-      </c>
-      <c r="CD4" s="147"/>
-      <c r="CE4" s="147"/>
-      <c r="CF4" s="147"/>
-      <c r="CG4" s="147"/>
-      <c r="CH4" s="147"/>
-      <c r="CI4" s="147"/>
-      <c r="CJ4" s="147">
+        <v>46076</v>
+      </c>
+      <c r="CD4" s="174"/>
+      <c r="CE4" s="174"/>
+      <c r="CF4" s="174"/>
+      <c r="CG4" s="174"/>
+      <c r="CH4" s="174"/>
+      <c r="CI4" s="174"/>
+      <c r="CJ4" s="174">
         <f ca="1">CL5</f>
-        <v>46048</v>
-      </c>
-      <c r="CK4" s="147"/>
-      <c r="CL4" s="147"/>
-      <c r="CM4" s="147"/>
-      <c r="CN4" s="147"/>
-      <c r="CO4" s="147"/>
-      <c r="CP4" s="147"/>
-      <c r="CQ4" s="147">
+        <v>46083</v>
+      </c>
+      <c r="CK4" s="174"/>
+      <c r="CL4" s="174"/>
+      <c r="CM4" s="174"/>
+      <c r="CN4" s="174"/>
+      <c r="CO4" s="174"/>
+      <c r="CP4" s="174"/>
+      <c r="CQ4" s="174">
         <f ca="1">CS5</f>
-        <v>46055</v>
-      </c>
-      <c r="CR4" s="147"/>
-      <c r="CS4" s="147"/>
-      <c r="CT4" s="147"/>
-      <c r="CU4" s="147"/>
-      <c r="CV4" s="147"/>
-      <c r="CW4" s="147"/>
-      <c r="CX4" s="147">
+        <v>46090</v>
+      </c>
+      <c r="CR4" s="174"/>
+      <c r="CS4" s="174"/>
+      <c r="CT4" s="174"/>
+      <c r="CU4" s="174"/>
+      <c r="CV4" s="174"/>
+      <c r="CW4" s="174"/>
+      <c r="CX4" s="174">
         <f ca="1">CZ5</f>
-        <v>46062</v>
-      </c>
-      <c r="CY4" s="147"/>
-      <c r="CZ4" s="147"/>
-      <c r="DA4" s="147"/>
-      <c r="DB4" s="147"/>
-      <c r="DC4" s="147"/>
-      <c r="DD4" s="147"/>
-      <c r="DE4" s="147">
+        <v>46097</v>
+      </c>
+      <c r="CY4" s="174"/>
+      <c r="CZ4" s="174"/>
+      <c r="DA4" s="174"/>
+      <c r="DB4" s="174"/>
+      <c r="DC4" s="174"/>
+      <c r="DD4" s="174"/>
+      <c r="DE4" s="174">
         <f ca="1">DG5</f>
-        <v>46069</v>
-      </c>
-      <c r="DF4" s="147"/>
-      <c r="DG4" s="147"/>
-      <c r="DH4" s="147"/>
-      <c r="DI4" s="147"/>
-      <c r="DJ4" s="147"/>
-      <c r="DK4" s="147"/>
-      <c r="DL4" s="147">
+        <v>46104</v>
+      </c>
+      <c r="DF4" s="174"/>
+      <c r="DG4" s="174"/>
+      <c r="DH4" s="174"/>
+      <c r="DI4" s="174"/>
+      <c r="DJ4" s="174"/>
+      <c r="DK4" s="174"/>
+      <c r="DL4" s="174">
         <f ca="1">DN5</f>
-        <v>46076</v>
-      </c>
-      <c r="DM4" s="147"/>
-      <c r="DN4" s="147"/>
-      <c r="DO4" s="147"/>
-      <c r="DP4" s="147"/>
-      <c r="DQ4" s="147"/>
-      <c r="DR4" s="147"/>
-      <c r="DS4" s="147">
+        <v>46111</v>
+      </c>
+      <c r="DM4" s="174"/>
+      <c r="DN4" s="174"/>
+      <c r="DO4" s="174"/>
+      <c r="DP4" s="174"/>
+      <c r="DQ4" s="174"/>
+      <c r="DR4" s="174"/>
+      <c r="DS4" s="174">
         <f ca="1">DU5</f>
-        <v>46083</v>
-      </c>
-      <c r="DT4" s="147"/>
-      <c r="DU4" s="147"/>
-      <c r="DV4" s="147"/>
-      <c r="DW4" s="147"/>
-      <c r="DX4" s="147"/>
-      <c r="DY4" s="147"/>
-      <c r="DZ4" s="147">
+        <v>46118</v>
+      </c>
+      <c r="DT4" s="174"/>
+      <c r="DU4" s="174"/>
+      <c r="DV4" s="174"/>
+      <c r="DW4" s="174"/>
+      <c r="DX4" s="174"/>
+      <c r="DY4" s="174"/>
+      <c r="DZ4" s="174">
         <f ca="1">EB5</f>
-        <v>46090</v>
-      </c>
-      <c r="EA4" s="147"/>
-      <c r="EB4" s="147"/>
-      <c r="EC4" s="147"/>
-      <c r="ED4" s="147"/>
-      <c r="EE4" s="147"/>
-      <c r="EF4" s="147"/>
-      <c r="EG4" s="147">
+        <v>46125</v>
+      </c>
+      <c r="EA4" s="174"/>
+      <c r="EB4" s="174"/>
+      <c r="EC4" s="174"/>
+      <c r="ED4" s="174"/>
+      <c r="EE4" s="174"/>
+      <c r="EF4" s="174"/>
+      <c r="EG4" s="174">
         <f ca="1">EI5</f>
-        <v>46097</v>
-      </c>
-      <c r="EH4" s="147"/>
-      <c r="EI4" s="147"/>
-      <c r="EJ4" s="147"/>
-      <c r="EK4" s="147"/>
-      <c r="EL4" s="147"/>
-      <c r="EM4" s="147"/>
-      <c r="EN4" s="147">
+        <v>46132</v>
+      </c>
+      <c r="EH4" s="174"/>
+      <c r="EI4" s="174"/>
+      <c r="EJ4" s="174"/>
+      <c r="EK4" s="174"/>
+      <c r="EL4" s="174"/>
+      <c r="EM4" s="174"/>
+      <c r="EN4" s="174">
         <f ca="1">EP5</f>
-        <v>46104</v>
-      </c>
-      <c r="EO4" s="147"/>
-      <c r="EP4" s="147"/>
-      <c r="EQ4" s="147"/>
-      <c r="ER4" s="147"/>
-      <c r="ES4" s="147"/>
-      <c r="ET4" s="147"/>
-      <c r="EU4" s="147">
+        <v>46139</v>
+      </c>
+      <c r="EO4" s="174"/>
+      <c r="EP4" s="174"/>
+      <c r="EQ4" s="174"/>
+      <c r="ER4" s="174"/>
+      <c r="ES4" s="174"/>
+      <c r="ET4" s="174"/>
+      <c r="EU4" s="174">
         <f ca="1">EW5</f>
-        <v>46111</v>
-      </c>
-      <c r="EV4" s="147"/>
-      <c r="EW4" s="147"/>
-      <c r="EX4" s="147"/>
-      <c r="EY4" s="147"/>
-      <c r="EZ4" s="147"/>
-      <c r="FA4" s="147"/>
-      <c r="FB4" s="147">
+        <v>46146</v>
+      </c>
+      <c r="EV4" s="174"/>
+      <c r="EW4" s="174"/>
+      <c r="EX4" s="174"/>
+      <c r="EY4" s="174"/>
+      <c r="EZ4" s="174"/>
+      <c r="FA4" s="174"/>
+      <c r="FB4" s="174">
         <f ca="1">FD5</f>
-        <v>46118</v>
-      </c>
-      <c r="FC4" s="147"/>
-      <c r="FD4" s="147"/>
-      <c r="FE4" s="147"/>
-      <c r="FF4" s="147"/>
-      <c r="FG4" s="147"/>
-      <c r="FH4" s="147"/>
-      <c r="FI4" s="147">
+        <v>46153</v>
+      </c>
+      <c r="FC4" s="174"/>
+      <c r="FD4" s="174"/>
+      <c r="FE4" s="174"/>
+      <c r="FF4" s="174"/>
+      <c r="FG4" s="174"/>
+      <c r="FH4" s="174"/>
+      <c r="FI4" s="174">
         <f ca="1">FK5</f>
-        <v>46125</v>
-      </c>
-      <c r="FJ4" s="147"/>
-      <c r="FK4" s="147"/>
-      <c r="FL4" s="147"/>
-      <c r="FM4" s="147"/>
-      <c r="FN4" s="147"/>
-      <c r="FO4" s="147"/>
-      <c r="FP4" s="147">
+        <v>46160</v>
+      </c>
+      <c r="FJ4" s="174"/>
+      <c r="FK4" s="174"/>
+      <c r="FL4" s="174"/>
+      <c r="FM4" s="174"/>
+      <c r="FN4" s="174"/>
+      <c r="FO4" s="174"/>
+      <c r="FP4" s="174">
         <f ca="1">FR5</f>
-        <v>46132</v>
-      </c>
-      <c r="FQ4" s="147"/>
-      <c r="FR4" s="147"/>
-      <c r="FS4" s="147"/>
-      <c r="FT4" s="147"/>
-      <c r="FU4" s="147"/>
-      <c r="FV4" s="147"/>
-      <c r="FW4" s="147">
+        <v>46167</v>
+      </c>
+      <c r="FQ4" s="174"/>
+      <c r="FR4" s="174"/>
+      <c r="FS4" s="174"/>
+      <c r="FT4" s="174"/>
+      <c r="FU4" s="174"/>
+      <c r="FV4" s="174"/>
+      <c r="FW4" s="174">
         <f ca="1">FY5</f>
-        <v>46139</v>
-      </c>
-      <c r="FX4" s="147"/>
-      <c r="FY4" s="147"/>
-      <c r="FZ4" s="147"/>
-      <c r="GA4" s="147"/>
-      <c r="GB4" s="147"/>
-      <c r="GC4" s="147"/>
-      <c r="GD4" s="147">
+        <v>46174</v>
+      </c>
+      <c r="FX4" s="174"/>
+      <c r="FY4" s="174"/>
+      <c r="FZ4" s="174"/>
+      <c r="GA4" s="174"/>
+      <c r="GB4" s="174"/>
+      <c r="GC4" s="174"/>
+      <c r="GD4" s="174">
         <f ca="1">GF5</f>
-        <v>46146</v>
-      </c>
-      <c r="GE4" s="147"/>
-      <c r="GF4" s="147"/>
-      <c r="GG4" s="147"/>
-      <c r="GH4" s="147"/>
-      <c r="GI4" s="147"/>
-      <c r="GJ4" s="147"/>
+        <v>46181</v>
+      </c>
+      <c r="GE4" s="174"/>
+      <c r="GF4" s="174"/>
+      <c r="GG4" s="174"/>
+      <c r="GH4" s="174"/>
+      <c r="GI4" s="174"/>
+      <c r="GJ4" s="174"/>
     </row>
     <row r="5" spans="1:194" s="14" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="176" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="150" t="s">
+      <c r="B5" s="176" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="151" t="s">
+      <c r="C5" s="177" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="152" t="s">
+      <c r="D5" s="178" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="152" t="s">
+      <c r="E5" s="178" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="152" t="s">
+      <c r="F5" s="178" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="152" t="s">
+      <c r="G5" s="178" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="152" t="s">
+      <c r="H5" s="178" t="s">
         <v>13</v>
       </c>
       <c r="I5" s="50"/>
@@ -3543,736 +3524,736 @@
       <c r="L5" s="36"/>
       <c r="M5" s="19">
         <f ca="1">Project_Start-WEEKDAY(Project_Start,1)+2+7*(Display_Week-1)</f>
-        <v>45971</v>
+        <v>46006</v>
       </c>
       <c r="N5" s="19">
         <f ca="1">M5+1</f>
-        <v>45972</v>
+        <v>46007</v>
       </c>
       <c r="O5" s="19">
         <f t="shared" ref="O5:BB5" ca="1" si="0">N5+1</f>
-        <v>45973</v>
+        <v>46008</v>
       </c>
       <c r="P5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45974</v>
+        <v>46009</v>
       </c>
       <c r="Q5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45975</v>
+        <v>46010</v>
       </c>
       <c r="R5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45976</v>
+        <v>46011</v>
       </c>
       <c r="S5" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>45977</v>
+        <v>46012</v>
       </c>
       <c r="T5" s="21">
         <f ca="1">S5+1</f>
-        <v>45978</v>
+        <v>46013</v>
       </c>
       <c r="U5" s="19">
         <f ca="1">T5+1</f>
-        <v>45979</v>
+        <v>46014</v>
       </c>
       <c r="V5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45980</v>
+        <v>46015</v>
       </c>
       <c r="W5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45981</v>
+        <v>46016</v>
       </c>
       <c r="X5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45982</v>
+        <v>46017</v>
       </c>
       <c r="Y5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45983</v>
+        <v>46018</v>
       </c>
       <c r="Z5" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>45984</v>
+        <v>46019</v>
       </c>
       <c r="AA5" s="21">
         <f ca="1">Z5+1</f>
-        <v>45985</v>
+        <v>46020</v>
       </c>
       <c r="AB5" s="19">
         <f ca="1">AA5+1</f>
-        <v>45986</v>
+        <v>46021</v>
       </c>
       <c r="AC5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45987</v>
+        <v>46022</v>
       </c>
       <c r="AD5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45988</v>
+        <v>46023</v>
       </c>
       <c r="AE5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45989</v>
+        <v>46024</v>
       </c>
       <c r="AF5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45990</v>
+        <v>46025</v>
       </c>
       <c r="AG5" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>45991</v>
+        <v>46026</v>
       </c>
       <c r="AH5" s="21">
         <f ca="1">AG5+1</f>
-        <v>45992</v>
+        <v>46027</v>
       </c>
       <c r="AI5" s="19">
         <f ca="1">AH5+1</f>
-        <v>45993</v>
+        <v>46028</v>
       </c>
       <c r="AJ5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45994</v>
+        <v>46029</v>
       </c>
       <c r="AK5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45995</v>
+        <v>46030</v>
       </c>
       <c r="AL5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45996</v>
+        <v>46031</v>
       </c>
       <c r="AM5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45997</v>
+        <v>46032</v>
       </c>
       <c r="AN5" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>45998</v>
+        <v>46033</v>
       </c>
       <c r="AO5" s="21">
         <f ca="1">AN5+1</f>
-        <v>45999</v>
+        <v>46034</v>
       </c>
       <c r="AP5" s="19">
         <f ca="1">AO5+1</f>
-        <v>46000</v>
+        <v>46035</v>
       </c>
       <c r="AQ5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>46001</v>
+        <v>46036</v>
       </c>
       <c r="AR5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>46002</v>
+        <v>46037</v>
       </c>
       <c r="AS5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>46003</v>
+        <v>46038</v>
       </c>
       <c r="AT5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>46004</v>
+        <v>46039</v>
       </c>
       <c r="AU5" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>46005</v>
+        <v>46040</v>
       </c>
       <c r="AV5" s="21">
         <f ca="1">AU5+1</f>
-        <v>46006</v>
+        <v>46041</v>
       </c>
       <c r="AW5" s="19">
         <f ca="1">AV5+1</f>
-        <v>46007</v>
+        <v>46042</v>
       </c>
       <c r="AX5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>46008</v>
+        <v>46043</v>
       </c>
       <c r="AY5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>46009</v>
+        <v>46044</v>
       </c>
       <c r="AZ5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>46010</v>
+        <v>46045</v>
       </c>
       <c r="BA5" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>46011</v>
+        <v>46046</v>
       </c>
       <c r="BB5" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>46012</v>
+        <v>46047</v>
       </c>
       <c r="BC5" s="21">
         <f ca="1">BB5+1</f>
-        <v>46013</v>
+        <v>46048</v>
       </c>
       <c r="BD5" s="19">
         <f ca="1">BC5+1</f>
-        <v>46014</v>
+        <v>46049</v>
       </c>
       <c r="BE5" s="19">
         <f t="shared" ref="BE5:BI5" ca="1" si="1">BD5+1</f>
-        <v>46015</v>
+        <v>46050</v>
       </c>
       <c r="BF5" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>46016</v>
+        <v>46051</v>
       </c>
       <c r="BG5" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>46017</v>
+        <v>46052</v>
       </c>
       <c r="BH5" s="19">
         <f t="shared" ca="1" si="1"/>
-        <v>46018</v>
+        <v>46053</v>
       </c>
       <c r="BI5" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>46019</v>
+        <v>46054</v>
       </c>
       <c r="BJ5" s="21">
         <f ca="1">BI5+1</f>
-        <v>46020</v>
+        <v>46055</v>
       </c>
       <c r="BK5" s="19">
         <f ca="1">BJ5+1</f>
-        <v>46021</v>
+        <v>46056</v>
       </c>
       <c r="BL5" s="19">
         <f t="shared" ref="BL5:BP5" ca="1" si="2">BK5+1</f>
-        <v>46022</v>
+        <v>46057</v>
       </c>
       <c r="BM5" s="19">
         <f t="shared" ca="1" si="2"/>
-        <v>46023</v>
+        <v>46058</v>
       </c>
       <c r="BN5" s="19">
         <f t="shared" ca="1" si="2"/>
-        <v>46024</v>
+        <v>46059</v>
       </c>
       <c r="BO5" s="19">
         <f t="shared" ca="1" si="2"/>
-        <v>46025</v>
+        <v>46060</v>
       </c>
       <c r="BP5" s="19">
         <f t="shared" ca="1" si="2"/>
-        <v>46026</v>
+        <v>46061</v>
       </c>
       <c r="BQ5" s="21">
         <f t="shared" ref="BQ5:CV5" ca="1" si="3">BP5+1</f>
-        <v>46027</v>
+        <v>46062</v>
       </c>
       <c r="BR5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46028</v>
+        <v>46063</v>
       </c>
       <c r="BS5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46029</v>
+        <v>46064</v>
       </c>
       <c r="BT5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46030</v>
+        <v>46065</v>
       </c>
       <c r="BU5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46031</v>
+        <v>46066</v>
       </c>
       <c r="BV5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46032</v>
+        <v>46067</v>
       </c>
       <c r="BW5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46033</v>
+        <v>46068</v>
       </c>
       <c r="BX5" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>46034</v>
+        <v>46069</v>
       </c>
       <c r="BY5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46035</v>
+        <v>46070</v>
       </c>
       <c r="BZ5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46036</v>
+        <v>46071</v>
       </c>
       <c r="CA5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46037</v>
+        <v>46072</v>
       </c>
       <c r="CB5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46038</v>
+        <v>46073</v>
       </c>
       <c r="CC5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46039</v>
+        <v>46074</v>
       </c>
       <c r="CD5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46040</v>
+        <v>46075</v>
       </c>
       <c r="CE5" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>46041</v>
+        <v>46076</v>
       </c>
       <c r="CF5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46042</v>
+        <v>46077</v>
       </c>
       <c r="CG5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46043</v>
+        <v>46078</v>
       </c>
       <c r="CH5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="CI5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46045</v>
+        <v>46080</v>
       </c>
       <c r="CJ5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46046</v>
+        <v>46081</v>
       </c>
       <c r="CK5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46047</v>
+        <v>46082</v>
       </c>
       <c r="CL5" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>46048</v>
+        <v>46083</v>
       </c>
       <c r="CM5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46049</v>
+        <v>46084</v>
       </c>
       <c r="CN5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46050</v>
+        <v>46085</v>
       </c>
       <c r="CO5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46051</v>
+        <v>46086</v>
       </c>
       <c r="CP5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46052</v>
+        <v>46087</v>
       </c>
       <c r="CQ5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46053</v>
+        <v>46088</v>
       </c>
       <c r="CR5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46054</v>
+        <v>46089</v>
       </c>
       <c r="CS5" s="21">
         <f t="shared" ca="1" si="3"/>
-        <v>46055</v>
+        <v>46090</v>
       </c>
       <c r="CT5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46056</v>
+        <v>46091</v>
       </c>
       <c r="CU5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46057</v>
+        <v>46092</v>
       </c>
       <c r="CV5" s="19">
         <f t="shared" ca="1" si="3"/>
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="CW5" s="19">
         <f t="shared" ref="CW5:EB5" ca="1" si="4">CV5+1</f>
-        <v>46059</v>
+        <v>46094</v>
       </c>
       <c r="CX5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46060</v>
+        <v>46095</v>
       </c>
       <c r="CY5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46061</v>
+        <v>46096</v>
       </c>
       <c r="CZ5" s="21">
         <f t="shared" ca="1" si="4"/>
-        <v>46062</v>
+        <v>46097</v>
       </c>
       <c r="DA5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46063</v>
+        <v>46098</v>
       </c>
       <c r="DB5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46064</v>
+        <v>46099</v>
       </c>
       <c r="DC5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46065</v>
+        <v>46100</v>
       </c>
       <c r="DD5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46066</v>
+        <v>46101</v>
       </c>
       <c r="DE5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46067</v>
+        <v>46102</v>
       </c>
       <c r="DF5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46068</v>
+        <v>46103</v>
       </c>
       <c r="DG5" s="21">
         <f t="shared" ca="1" si="4"/>
-        <v>46069</v>
+        <v>46104</v>
       </c>
       <c r="DH5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46070</v>
+        <v>46105</v>
       </c>
       <c r="DI5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46071</v>
+        <v>46106</v>
       </c>
       <c r="DJ5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46072</v>
+        <v>46107</v>
       </c>
       <c r="DK5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46073</v>
+        <v>46108</v>
       </c>
       <c r="DL5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46074</v>
+        <v>46109</v>
       </c>
       <c r="DM5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46075</v>
+        <v>46110</v>
       </c>
       <c r="DN5" s="21">
         <f t="shared" ca="1" si="4"/>
-        <v>46076</v>
+        <v>46111</v>
       </c>
       <c r="DO5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46077</v>
+        <v>46112</v>
       </c>
       <c r="DP5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46078</v>
+        <v>46113</v>
       </c>
       <c r="DQ5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46079</v>
+        <v>46114</v>
       </c>
       <c r="DR5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46080</v>
+        <v>46115</v>
       </c>
       <c r="DS5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46081</v>
+        <v>46116</v>
       </c>
       <c r="DT5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46082</v>
+        <v>46117</v>
       </c>
       <c r="DU5" s="21">
         <f t="shared" ca="1" si="4"/>
-        <v>46083</v>
+        <v>46118</v>
       </c>
       <c r="DV5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46084</v>
+        <v>46119</v>
       </c>
       <c r="DW5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46085</v>
+        <v>46120</v>
       </c>
       <c r="DX5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46086</v>
+        <v>46121</v>
       </c>
       <c r="DY5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46087</v>
+        <v>46122</v>
       </c>
       <c r="DZ5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46088</v>
+        <v>46123</v>
       </c>
       <c r="EA5" s="19">
         <f t="shared" ca="1" si="4"/>
-        <v>46089</v>
+        <v>46124</v>
       </c>
       <c r="EB5" s="21">
         <f t="shared" ca="1" si="4"/>
-        <v>46090</v>
+        <v>46125</v>
       </c>
       <c r="EC5" s="19">
         <f t="shared" ref="EC5:FH5" ca="1" si="5">EB5+1</f>
-        <v>46091</v>
+        <v>46126</v>
       </c>
       <c r="ED5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46092</v>
+        <v>46127</v>
       </c>
       <c r="EE5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46093</v>
+        <v>46128</v>
       </c>
       <c r="EF5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46094</v>
+        <v>46129</v>
       </c>
       <c r="EG5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46095</v>
+        <v>46130</v>
       </c>
       <c r="EH5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46096</v>
+        <v>46131</v>
       </c>
       <c r="EI5" s="21">
         <f t="shared" ca="1" si="5"/>
-        <v>46097</v>
+        <v>46132</v>
       </c>
       <c r="EJ5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46098</v>
+        <v>46133</v>
       </c>
       <c r="EK5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46099</v>
+        <v>46134</v>
       </c>
       <c r="EL5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46100</v>
+        <v>46135</v>
       </c>
       <c r="EM5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46101</v>
+        <v>46136</v>
       </c>
       <c r="EN5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46102</v>
+        <v>46137</v>
       </c>
       <c r="EO5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46103</v>
+        <v>46138</v>
       </c>
       <c r="EP5" s="21">
         <f t="shared" ca="1" si="5"/>
-        <v>46104</v>
+        <v>46139</v>
       </c>
       <c r="EQ5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46140</v>
       </c>
       <c r="ER5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46106</v>
+        <v>46141</v>
       </c>
       <c r="ES5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46107</v>
+        <v>46142</v>
       </c>
       <c r="ET5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46108</v>
+        <v>46143</v>
       </c>
       <c r="EU5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46109</v>
+        <v>46144</v>
       </c>
       <c r="EV5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46110</v>
+        <v>46145</v>
       </c>
       <c r="EW5" s="21">
         <f t="shared" ca="1" si="5"/>
-        <v>46111</v>
+        <v>46146</v>
       </c>
       <c r="EX5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46112</v>
+        <v>46147</v>
       </c>
       <c r="EY5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46113</v>
+        <v>46148</v>
       </c>
       <c r="EZ5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46114</v>
+        <v>46149</v>
       </c>
       <c r="FA5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46115</v>
+        <v>46150</v>
       </c>
       <c r="FB5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46116</v>
+        <v>46151</v>
       </c>
       <c r="FC5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46117</v>
+        <v>46152</v>
       </c>
       <c r="FD5" s="21">
         <f t="shared" ca="1" si="5"/>
-        <v>46118</v>
+        <v>46153</v>
       </c>
       <c r="FE5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46119</v>
+        <v>46154</v>
       </c>
       <c r="FF5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46120</v>
+        <v>46155</v>
       </c>
       <c r="FG5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46121</v>
+        <v>46156</v>
       </c>
       <c r="FH5" s="19">
         <f t="shared" ca="1" si="5"/>
-        <v>46122</v>
+        <v>46157</v>
       </c>
       <c r="FI5" s="19">
         <f t="shared" ref="FI5:GJ5" ca="1" si="6">FH5+1</f>
-        <v>46123</v>
+        <v>46158</v>
       </c>
       <c r="FJ5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46124</v>
+        <v>46159</v>
       </c>
       <c r="FK5" s="21">
         <f t="shared" ca="1" si="6"/>
-        <v>46125</v>
+        <v>46160</v>
       </c>
       <c r="FL5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46126</v>
+        <v>46161</v>
       </c>
       <c r="FM5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46127</v>
+        <v>46162</v>
       </c>
       <c r="FN5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46128</v>
+        <v>46163</v>
       </c>
       <c r="FO5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46129</v>
+        <v>46164</v>
       </c>
       <c r="FP5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46130</v>
+        <v>46165</v>
       </c>
       <c r="FQ5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46131</v>
+        <v>46166</v>
       </c>
       <c r="FR5" s="21">
         <f t="shared" ca="1" si="6"/>
-        <v>46132</v>
+        <v>46167</v>
       </c>
       <c r="FS5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46133</v>
+        <v>46168</v>
       </c>
       <c r="FT5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46134</v>
+        <v>46169</v>
       </c>
       <c r="FU5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46135</v>
+        <v>46170</v>
       </c>
       <c r="FV5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46136</v>
+        <v>46171</v>
       </c>
       <c r="FW5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46137</v>
+        <v>46172</v>
       </c>
       <c r="FX5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46138</v>
+        <v>46173</v>
       </c>
       <c r="FY5" s="21">
         <f t="shared" ca="1" si="6"/>
-        <v>46139</v>
+        <v>46174</v>
       </c>
       <c r="FZ5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46140</v>
+        <v>46175</v>
       </c>
       <c r="GA5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46141</v>
+        <v>46176</v>
       </c>
       <c r="GB5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46142</v>
+        <v>46177</v>
       </c>
       <c r="GC5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46143</v>
+        <v>46178</v>
       </c>
       <c r="GD5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46144</v>
+        <v>46179</v>
       </c>
       <c r="GE5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46145</v>
+        <v>46180</v>
       </c>
       <c r="GF5" s="21">
         <f t="shared" ca="1" si="6"/>
-        <v>46146</v>
+        <v>46181</v>
       </c>
       <c r="GG5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46147</v>
+        <v>46182</v>
       </c>
       <c r="GH5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46148</v>
+        <v>46183</v>
       </c>
       <c r="GI5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46149</v>
+        <v>46184</v>
       </c>
       <c r="GJ5" s="19">
         <f t="shared" ca="1" si="6"/>
-        <v>46150</v>
+        <v>46185</v>
       </c>
       <c r="GK5" s="19"/>
       <c r="GL5" s="19"/>
     </row>
     <row r="6" spans="1:194" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="150"/>
-      <c r="B6" s="150"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152"/>
-      <c r="H6" s="152"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="176"/>
+      <c r="C6" s="177"/>
+      <c r="D6" s="178"/>
+      <c r="E6" s="178"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="178"/>
+      <c r="H6" s="178"/>
       <c r="I6" s="38"/>
       <c r="J6" s="39"/>
       <c r="K6" s="36"/>
@@ -5269,10 +5250,10 @@
       <c r="GJ8" s="42"/>
     </row>
     <row r="9" spans="1:194" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A9" s="155" t="s">
+      <c r="A9" s="166" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="167" t="s">
+      <c r="B9" s="154" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="129" t="s">
@@ -5287,7 +5268,7 @@
       <c r="F9" s="118">
         <v>45976</v>
       </c>
-      <c r="G9" s="177" t="s">
+      <c r="G9" s="164" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="102" t="s">
@@ -5481,8 +5462,8 @@
       <c r="GJ9" s="112"/>
     </row>
     <row r="10" spans="1:194" s="114" customFormat="1" ht="87" customHeight="1" thickBot="1">
-      <c r="A10" s="155"/>
-      <c r="B10" s="167"/>
+      <c r="A10" s="166"/>
+      <c r="B10" s="154"/>
       <c r="C10" s="132" t="s">
         <v>16</v>
       </c>
@@ -5495,7 +5476,7 @@
       <c r="F10" s="126">
         <v>45968</v>
       </c>
-      <c r="G10" s="178"/>
+      <c r="G10" s="165"/>
       <c r="H10" s="107" t="s">
         <v>19</v>
       </c>
@@ -5681,8 +5662,8 @@
       <c r="GJ10" s="112"/>
     </row>
     <row r="11" spans="1:194" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A11" s="155"/>
-      <c r="B11" s="167"/>
+      <c r="A11" s="166"/>
+      <c r="B11" s="154"/>
       <c r="C11" s="133" t="s">
         <v>16</v>
       </c>
@@ -5695,7 +5676,7 @@
       <c r="F11" s="125">
         <v>45968</v>
       </c>
-      <c r="G11" s="178"/>
+      <c r="G11" s="165"/>
       <c r="H11" s="102" t="s">
         <v>20</v>
       </c>
@@ -5885,9 +5866,9 @@
       <c r="GI11" s="34"/>
       <c r="GJ11" s="34"/>
     </row>
-    <row r="12" spans="1:194" s="28" customFormat="1" ht="53.25" thickBot="1">
-      <c r="A12" s="155"/>
-      <c r="B12" s="168"/>
+    <row r="12" spans="1:194" s="28" customFormat="1" ht="70.5">
+      <c r="A12" s="166"/>
+      <c r="B12" s="155"/>
       <c r="C12" s="104" t="s">
         <v>16</v>
       </c>
@@ -6094,11 +6075,11 @@
       <c r="GI12" s="34"/>
       <c r="GJ12" s="34"/>
     </row>
-    <row r="13" spans="1:194" s="28" customFormat="1" ht="106.15" thickBot="1">
-      <c r="A13" s="156" t="s">
+    <row r="13" spans="1:194" s="28" customFormat="1" ht="105.75">
+      <c r="A13" s="167" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="169" t="s">
+      <c r="B13" s="156" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="87" t="s">
@@ -6302,19 +6283,19 @@
       <c r="GJ13" s="34"/>
     </row>
     <row r="14" spans="1:194" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A14" s="156"/>
-      <c r="B14" s="169"/>
+      <c r="A14" s="167"/>
+      <c r="B14" s="156"/>
       <c r="C14" s="121" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D14" s="88"/>
       <c r="E14" s="89"/>
       <c r="F14" s="89"/>
-      <c r="G14" s="171" t="s">
+      <c r="G14" s="158" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="119" t="s">
         <v>29</v>
-      </c>
-      <c r="H14" s="119" t="s">
-        <v>30</v>
       </c>
       <c r="I14" s="36"/>
       <c r="J14" s="3"/>
@@ -6502,17 +6483,17 @@
       <c r="GJ14" s="29"/>
     </row>
     <row r="15" spans="1:194" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A15" s="156"/>
-      <c r="B15" s="169"/>
+      <c r="A15" s="167"/>
+      <c r="B15" s="156"/>
       <c r="C15" s="120" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="88"/>
       <c r="E15" s="89"/>
       <c r="F15" s="89"/>
-      <c r="G15" s="172"/>
+      <c r="G15" s="159"/>
       <c r="H15" s="101" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I15" s="36"/>
       <c r="J15" s="3"/>
@@ -6700,17 +6681,17 @@
       <c r="GJ15" s="29"/>
     </row>
     <row r="16" spans="1:194" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A16" s="156"/>
-      <c r="B16" s="169"/>
+      <c r="A16" s="167"/>
+      <c r="B16" s="156"/>
       <c r="C16" s="87" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" s="88"/>
       <c r="E16" s="90"/>
       <c r="F16" s="91"/>
-      <c r="G16" s="173"/>
+      <c r="G16" s="160"/>
       <c r="H16" s="101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I16" s="36"/>
       <c r="J16" s="3" t="str">
@@ -6901,19 +6882,19 @@
       <c r="GJ16" s="141"/>
     </row>
     <row r="17" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A17" s="156"/>
-      <c r="B17" s="169"/>
+      <c r="A17" s="167"/>
+      <c r="B17" s="156"/>
       <c r="C17" s="87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" s="88"/>
       <c r="E17" s="89"/>
       <c r="F17" s="89"/>
       <c r="G17" s="113" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="119" t="s">
         <v>35</v>
-      </c>
-      <c r="H17" s="119" t="s">
-        <v>36</v>
       </c>
       <c r="I17" s="36"/>
       <c r="J17" s="3" t="str">
@@ -7104,10 +7085,10 @@
       <c r="GJ17" s="34"/>
     </row>
     <row r="18" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A18" s="156"/>
-      <c r="B18" s="169"/>
+      <c r="A18" s="167"/>
+      <c r="B18" s="156"/>
       <c r="C18" s="87" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" s="88"/>
       <c r="E18" s="89"/>
@@ -7307,10 +7288,10 @@
       <c r="GJ18" s="34"/>
     </row>
     <row r="19" spans="1:193" s="28" customFormat="1" ht="88.5" thickBot="1">
-      <c r="A19" s="157" t="s">
+      <c r="A19" s="168" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="166" t="s">
+      <c r="B19" s="153" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="78" t="s">
@@ -7319,7 +7300,7 @@
       <c r="D19" s="79"/>
       <c r="E19" s="80"/>
       <c r="F19" s="80"/>
-      <c r="G19" s="174" t="s">
+      <c r="G19" s="161" t="s">
         <v>42</v>
       </c>
       <c r="H19" s="122" t="s">
@@ -7514,15 +7495,15 @@
       <c r="GJ19" s="34"/>
     </row>
     <row r="20" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A20" s="157"/>
-      <c r="B20" s="166"/>
+      <c r="A20" s="168"/>
+      <c r="B20" s="153"/>
       <c r="C20" s="78" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="79"/>
       <c r="E20" s="80"/>
       <c r="F20" s="80"/>
-      <c r="G20" s="175"/>
+      <c r="G20" s="162"/>
       <c r="H20" s="122" t="s">
         <v>45</v>
       </c>
@@ -7715,15 +7696,15 @@
       <c r="GJ20" s="34"/>
     </row>
     <row r="21" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A21" s="157"/>
-      <c r="B21" s="166"/>
+      <c r="A21" s="168"/>
+      <c r="B21" s="153"/>
       <c r="C21" s="78" t="s">
         <v>44</v>
       </c>
       <c r="D21" s="79"/>
       <c r="E21" s="80"/>
       <c r="F21" s="80"/>
-      <c r="G21" s="175"/>
+      <c r="G21" s="162"/>
       <c r="H21" s="122" t="s">
         <v>46</v>
       </c>
@@ -7916,15 +7897,15 @@
       <c r="GJ21" s="34"/>
     </row>
     <row r="22" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A22" s="157"/>
-      <c r="B22" s="166"/>
+      <c r="A22" s="168"/>
+      <c r="B22" s="153"/>
       <c r="C22" s="78" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="79"/>
       <c r="E22" s="81"/>
       <c r="F22" s="82"/>
-      <c r="G22" s="176"/>
+      <c r="G22" s="163"/>
       <c r="H22" s="99" t="s">
         <v>47</v>
       </c>
@@ -8117,15 +8098,15 @@
       <c r="GJ22" s="34"/>
     </row>
     <row r="23" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A23" s="157"/>
-      <c r="B23" s="166"/>
+      <c r="A23" s="168"/>
+      <c r="B23" s="153"/>
       <c r="C23" s="78" t="s">
         <v>44</v>
       </c>
       <c r="D23" s="79"/>
       <c r="E23" s="80"/>
       <c r="F23" s="80"/>
-      <c r="G23" s="175" t="s">
+      <c r="G23" s="162" t="s">
         <v>48</v>
       </c>
       <c r="H23" s="123" t="s">
@@ -8319,16 +8300,16 @@
       <c r="GI23" s="34"/>
       <c r="GJ23" s="34"/>
     </row>
-    <row r="24" spans="1:193" s="28" customFormat="1" ht="52.5" thickBot="1">
-      <c r="A24" s="157"/>
-      <c r="B24" s="166"/>
+    <row r="24" spans="1:193" s="28" customFormat="1" ht="53.25" thickBot="1">
+      <c r="A24" s="168"/>
+      <c r="B24" s="153"/>
       <c r="C24" s="78" t="s">
         <v>44</v>
       </c>
       <c r="D24" s="79"/>
       <c r="E24" s="80"/>
       <c r="F24" s="80"/>
-      <c r="G24" s="175"/>
+      <c r="G24" s="162"/>
       <c r="H24" s="122" t="s">
         <v>50</v>
       </c>
@@ -8521,15 +8502,15 @@
       <c r="GJ24" s="34"/>
     </row>
     <row r="25" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A25" s="157"/>
-      <c r="B25" s="166"/>
+      <c r="A25" s="168"/>
+      <c r="B25" s="153"/>
       <c r="C25" s="78" t="s">
         <v>51</v>
       </c>
       <c r="D25" s="79"/>
       <c r="E25" s="80"/>
       <c r="F25" s="80"/>
-      <c r="G25" s="176"/>
+      <c r="G25" s="163"/>
       <c r="H25" s="134" t="s">
         <v>52</v>
       </c>
@@ -8722,10 +8703,10 @@
       <c r="GJ25" s="34"/>
     </row>
     <row r="26" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A26" s="158" t="s">
+      <c r="A26" s="169" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="170" t="s">
+      <c r="B26" s="157" t="s">
         <v>54</v>
       </c>
       <c r="C26" s="92" t="s">
@@ -8734,7 +8715,7 @@
       <c r="D26" s="93"/>
       <c r="E26" s="94"/>
       <c r="F26" s="94"/>
-      <c r="G26" s="163" t="s">
+      <c r="G26" s="150" t="s">
         <v>56</v>
       </c>
       <c r="H26" s="140" t="s">
@@ -8929,15 +8910,15 @@
       <c r="GJ26" s="34"/>
     </row>
     <row r="27" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A27" s="158"/>
-      <c r="B27" s="170"/>
+      <c r="A27" s="169"/>
+      <c r="B27" s="157"/>
       <c r="C27" s="92" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D27" s="93"/>
       <c r="E27" s="94"/>
       <c r="F27" s="94"/>
-      <c r="G27" s="164"/>
+      <c r="G27" s="151"/>
       <c r="H27" s="135" t="s">
         <v>58</v>
       </c>
@@ -9130,15 +9111,15 @@
       <c r="GJ27" s="34"/>
     </row>
     <row r="28" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A28" s="158"/>
-      <c r="B28" s="170"/>
+      <c r="A28" s="169"/>
+      <c r="B28" s="157"/>
       <c r="C28" s="92" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D28" s="93"/>
       <c r="E28" s="95"/>
       <c r="F28" s="96"/>
-      <c r="G28" s="165"/>
+      <c r="G28" s="152"/>
       <c r="H28" s="135" t="s">
         <v>59</v>
       </c>
@@ -9332,19 +9313,19 @@
       <c r="GK28" s="141"/>
     </row>
     <row r="29" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A29" s="158"/>
-      <c r="B29" s="170"/>
+      <c r="A29" s="169"/>
+      <c r="B29" s="157"/>
       <c r="C29" s="92" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D29" s="93"/>
       <c r="E29" s="94"/>
       <c r="F29" s="94"/>
       <c r="G29" s="143" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H29" s="135" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I29" s="36"/>
       <c r="J29" s="3" t="str">
@@ -9536,8 +9517,8 @@
       <c r="GK29" s="141"/>
     </row>
     <row r="30" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A30" s="158"/>
-      <c r="B30" s="170"/>
+      <c r="A30" s="169"/>
+      <c r="B30" s="157"/>
       <c r="C30" s="92" t="s">
         <v>41</v>
       </c>
@@ -9548,7 +9529,7 @@
         <v>56</v>
       </c>
       <c r="H30" s="136" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I30" s="36"/>
       <c r="J30" s="3" t="str">
@@ -9740,11 +9721,11 @@
       <c r="GK30" s="141"/>
     </row>
     <row r="31" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A31" s="159" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="160" t="s">
+      <c r="A31" s="170" t="s">
         <v>64</v>
+      </c>
+      <c r="B31" s="147" t="s">
+        <v>65</v>
       </c>
       <c r="C31" s="83" t="s">
         <v>41</v>
@@ -9753,10 +9734,10 @@
       <c r="E31" s="85"/>
       <c r="F31" s="85"/>
       <c r="G31" s="139" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H31" s="124" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I31" s="36"/>
       <c r="J31" s="3" t="str">
@@ -9948,8 +9929,8 @@
       <c r="GK31" s="141"/>
     </row>
     <row r="32" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A32" s="159"/>
-      <c r="B32" s="161"/>
+      <c r="A32" s="170"/>
+      <c r="B32" s="148"/>
       <c r="C32" s="83" t="s">
         <v>41</v>
       </c>
@@ -9957,10 +9938,10 @@
       <c r="E32" s="85"/>
       <c r="F32" s="85"/>
       <c r="G32" s="139" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H32" s="124" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I32" s="36"/>
       <c r="J32" s="3" t="str">
@@ -10152,8 +10133,8 @@
       <c r="GK32" s="141"/>
     </row>
     <row r="33" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A33" s="159"/>
-      <c r="B33" s="161"/>
+      <c r="A33" s="170"/>
+      <c r="B33" s="148"/>
       <c r="C33" s="83" t="s">
         <v>41</v>
       </c>
@@ -10161,10 +10142,10 @@
       <c r="E33" s="85"/>
       <c r="F33" s="85"/>
       <c r="G33" s="139" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H33" s="124" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I33" s="36"/>
       <c r="J33" s="3" t="str">
@@ -10356,8 +10337,8 @@
       <c r="GK33" s="141"/>
     </row>
     <row r="34" spans="1:193" s="28" customFormat="1" ht="88.15" customHeight="1" thickBot="1">
-      <c r="A34" s="159"/>
-      <c r="B34" s="161"/>
+      <c r="A34" s="170"/>
+      <c r="B34" s="148"/>
       <c r="C34" s="83" t="s">
         <v>41</v>
       </c>
@@ -10365,10 +10346,10 @@
       <c r="E34" s="85"/>
       <c r="F34" s="85"/>
       <c r="G34" s="139" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H34" s="124" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I34" s="36"/>
       <c r="J34" s="3" t="str">
@@ -10560,8 +10541,8 @@
       <c r="GK34" s="141"/>
     </row>
     <row r="35" spans="1:193" s="28" customFormat="1" ht="106.15" thickBot="1">
-      <c r="A35" s="159"/>
-      <c r="B35" s="161"/>
+      <c r="A35" s="170"/>
+      <c r="B35" s="148"/>
       <c r="C35" s="137" t="s">
         <v>41</v>
       </c>
@@ -10569,10 +10550,10 @@
       <c r="E35" s="97"/>
       <c r="F35" s="86"/>
       <c r="G35" s="139" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H35" s="124" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I35" s="36"/>
       <c r="J35" s="4" t="str">
@@ -10764,8 +10745,8 @@
       <c r="GK35" s="141"/>
     </row>
     <row r="36" spans="1:193" ht="88.15" customHeight="1">
-      <c r="A36" s="159"/>
-      <c r="B36" s="162"/>
+      <c r="A36" s="170"/>
+      <c r="B36" s="149"/>
       <c r="C36" s="138" t="s">
         <v>41</v>
       </c>
@@ -10773,10 +10754,10 @@
       <c r="E36" s="98"/>
       <c r="F36" s="98"/>
       <c r="G36" s="144" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H36" s="124" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I36" s="36"/>
       <c r="K36" s="34"/>
@@ -11121,45 +11102,6 @@
   </sheetData>
   <autoFilter ref="A8:H36" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="55">
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="B19:B25"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="G19:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="A26:A30"/>
-    <mergeCell ref="A31:A36"/>
-    <mergeCell ref="S2:AB2"/>
-    <mergeCell ref="S1:AB1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="BH4:BN4"/>
-    <mergeCell ref="K4:Q4"/>
-    <mergeCell ref="R4:X4"/>
-    <mergeCell ref="Y4:AE4"/>
-    <mergeCell ref="AF4:AL4"/>
-    <mergeCell ref="AM4:AS4"/>
-    <mergeCell ref="AT4:AZ4"/>
-    <mergeCell ref="BA4:BG4"/>
-    <mergeCell ref="BV4:CB4"/>
-    <mergeCell ref="CC4:CI4"/>
-    <mergeCell ref="CJ4:CP4"/>
-    <mergeCell ref="CQ4:CW4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="FP4:FV4"/>
     <mergeCell ref="FW4:GC4"/>
     <mergeCell ref="GD4:GJ4"/>
@@ -11176,6 +11118,45 @@
     <mergeCell ref="DS4:DY4"/>
     <mergeCell ref="DZ4:EF4"/>
     <mergeCell ref="BO4:BU4"/>
+    <mergeCell ref="BV4:CB4"/>
+    <mergeCell ref="CC4:CI4"/>
+    <mergeCell ref="CJ4:CP4"/>
+    <mergeCell ref="CQ4:CW4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="S2:AB2"/>
+    <mergeCell ref="S1:AB1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="BH4:BN4"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="Y4:AE4"/>
+    <mergeCell ref="AF4:AL4"/>
+    <mergeCell ref="AM4:AS4"/>
+    <mergeCell ref="AT4:AZ4"/>
+    <mergeCell ref="BA4:BG4"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="B19:B25"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G9:G11"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D35">
     <cfRule type="dataBar" priority="316">
@@ -11191,18 +11172,12 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O14:P18 K11:K33 L14:GJ16">
-    <cfRule type="expression" dxfId="33" priority="300" stopIfTrue="1">
-      <formula>AND(task_end&gt;=M$5,task_start&lt;N$5)</formula>
+  <conditionalFormatting sqref="K11:K33 L9:GJ16">
+    <cfRule type="expression" dxfId="31" priority="38">
+      <formula>AND(task_start&lt;=M$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=M$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33">
-    <cfRule type="expression" dxfId="32" priority="14">
-      <formula>AND(task_start&lt;=M$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=M$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="15" stopIfTrue="1">
-      <formula>AND(task_end&gt;=M$5,task_start&lt;N$5)</formula>
-    </cfRule>
     <cfRule type="expression" dxfId="30" priority="16">
       <formula>AND(task_start&lt;=M$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=M$5)</formula>
     </cfRule>
@@ -11210,139 +11185,129 @@
       <formula>AND(task_end&gt;=M$5,task_start&lt;N$5)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K33:K36">
+    <cfRule type="expression" dxfId="28" priority="9">
+      <formula>AND(task_start&lt;=M$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=M$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="10" stopIfTrue="1">
+      <formula>AND(task_end&gt;=M$5,task_start&lt;N$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K34:K36">
+    <cfRule type="expression" dxfId="26" priority="7">
+      <formula>AND(task_start&lt;=M$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=M$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="8" stopIfTrue="1">
+      <formula>AND(task_end&gt;=M$5,task_start&lt;N$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="11">
+      <formula>AND(task_start&lt;=M$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=M$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="12">
+      <formula>AND(TODAY()&gt;=M$5, TODAY()&lt;N$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="13" stopIfTrue="1">
+      <formula>AND(task_end&gt;=M$5,task_start&lt;N$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L17:BN21">
-    <cfRule type="expression" dxfId="28" priority="298" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="298" stopIfTrue="1">
       <formula>AND(task_end&gt;=N$5,task_start&lt;O$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23:BN27">
-    <cfRule type="expression" dxfId="27" priority="296" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="296" stopIfTrue="1">
+      <formula>AND(task_end&gt;=N$5,task_start&lt;O$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L22:BU22">
+    <cfRule type="expression" dxfId="19" priority="3">
+      <formula>AND(task_start&lt;=N$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=N$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="4" stopIfTrue="1">
       <formula>AND(task_end&gt;=N$5,task_start&lt;O$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L9:GJ13">
-    <cfRule type="expression" dxfId="26" priority="33">
+    <cfRule type="expression" dxfId="17" priority="33">
       <formula>AND(TODAY()&gt;=N$5, TODAY()&lt;O$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="39" stopIfTrue="1">
       <formula>AND(task_end&gt;=N$5,task_start&lt;O$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L9:GJ15 K11:K33">
-    <cfRule type="expression" dxfId="24" priority="38">
-      <formula>AND(task_start&lt;=M$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=M$5)</formula>
+  <conditionalFormatting sqref="L14:GJ16 O14:P18 K11:K33">
+    <cfRule type="expression" dxfId="15" priority="300" stopIfTrue="1">
+      <formula>AND(task_end&gt;=M$5,task_start&lt;N$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BO4:GJ4 K7:BN8 K11:K33 L28:GK36 L14:GJ27">
-    <cfRule type="expression" dxfId="23" priority="294">
+  <conditionalFormatting sqref="L14:GJ27 K11:K33 L28:GK36 BO4:GJ4 K7:BN8">
+    <cfRule type="expression" dxfId="14" priority="294">
       <formula>AND(TODAY()&gt;=M$5, TODAY()&lt;N$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L17:GJ21">
-    <cfRule type="expression" dxfId="22" priority="36">
+    <cfRule type="expression" dxfId="13" priority="36">
       <formula>AND(task_start&lt;=N$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=N$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23:GJ27">
-    <cfRule type="expression" dxfId="21" priority="34">
+    <cfRule type="expression" dxfId="12" priority="34">
       <formula>AND(task_start&lt;=N$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=N$5)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L28:GK36">
+    <cfRule type="expression" dxfId="11" priority="5">
+      <formula>AND(task_start&lt;=N$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=N$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="6" stopIfTrue="1">
+      <formula>AND(task_end&gt;=N$5,task_start&lt;O$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M5:GL6">
-    <cfRule type="expression" dxfId="20" priority="293">
+    <cfRule type="expression" dxfId="9" priority="293">
       <formula>AND(TODAY()&gt;=M$5, TODAY()&lt;N$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O23:O27">
-    <cfRule type="expression" dxfId="19" priority="20">
+    <cfRule type="expression" dxfId="8" priority="21" stopIfTrue="1">
+      <formula>AND(task_end&gt;=Q$5,task_start&lt;R$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="20">
       <formula>AND(task_start&lt;=Q$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=Q$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="21" stopIfTrue="1">
-      <formula>AND(task_end&gt;=Q$5,task_start&lt;R$5)</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O14:P18 L16:GJ16">
-    <cfRule type="expression" dxfId="17" priority="299">
-      <formula>AND(task_start&lt;=N$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=N$5)</formula>
+  <conditionalFormatting sqref="O14:P18">
+    <cfRule type="expression" dxfId="6" priority="299">
+      <formula>AND(task_start&lt;=Q$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=Q$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BO8:DK8">
-    <cfRule type="expression" dxfId="16" priority="23">
+    <cfRule type="expression" dxfId="5" priority="23">
       <formula>AND(TODAY()&gt;=BQ$5, TODAY()&lt;BR$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BO17:GJ21">
-    <cfRule type="expression" dxfId="15" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="37" stopIfTrue="1">
       <formula>AND(task_end&gt;=BQ$5,task_start&lt;BR$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BO23:GJ27">
-    <cfRule type="expression" dxfId="14" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="35" stopIfTrue="1">
       <formula>AND(task_end&gt;=BQ$5,task_start&lt;BR$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DN8:GJ8">
-    <cfRule type="expression" dxfId="13" priority="22">
-      <formula>AND(TODAY()&gt;=DP$5, TODAY()&lt;DQ$5)</formula>
+  <conditionalFormatting sqref="BW22:GJ22">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
+      <formula>AND(task_end&gt;=BY$5,task_start&lt;BZ$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>AND(task_start&lt;=BY$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BY$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K34:K36">
-    <cfRule type="expression" dxfId="12" priority="13" stopIfTrue="1">
-      <formula>AND(task_end&gt;=M$5,task_start&lt;N$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K34:K36">
-    <cfRule type="expression" dxfId="11" priority="7">
-      <formula>AND(task_start&lt;=M$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=M$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="8" stopIfTrue="1">
-      <formula>AND(task_end&gt;=M$5,task_start&lt;N$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="9">
-      <formula>AND(task_start&lt;=M$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=M$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10" stopIfTrue="1">
-      <formula>AND(task_end&gt;=M$5,task_start&lt;N$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K34:K36">
-    <cfRule type="expression" dxfId="7" priority="11">
-      <formula>AND(task_start&lt;=M$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=M$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K34:K36">
-    <cfRule type="expression" dxfId="6" priority="12">
-      <formula>AND(TODAY()&gt;=M$5, TODAY()&lt;N$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L28:GK36">
-    <cfRule type="expression" dxfId="5" priority="6" stopIfTrue="1">
-      <formula>AND(task_end&gt;=N$5,task_start&lt;O$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L28:GK36">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>AND(task_start&lt;=N$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=N$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L22:BU22">
-    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
-      <formula>AND(task_end&gt;=N$5,task_start&lt;O$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L22:BU22">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>AND(task_start&lt;=N$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=N$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BW22:GJ22">
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
-      <formula>AND(task_end&gt;=BY$5,task_start&lt;BZ$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BW22:GJ22">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(task_start&lt;=BY$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BY$5)</formula>
+  <conditionalFormatting sqref="DN8:GJ8">
+    <cfRule type="expression" dxfId="0" priority="22">
+      <formula>AND(TODAY()&gt;=DP$5, TODAY()&lt;DQ$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -11353,7 +11318,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup scale="17" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="16" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter differentFirst="1" scaleWithDoc="0">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -11397,124 +11362,124 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15">
       <c r="A1" s="56" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B1" s="56" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1" s="56" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D1" s="56" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E1" s="56" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F1" s="56" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="27">
       <c r="A2" s="142" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" s="57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E2" s="60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="28.5">
+    <row r="3" spans="1:6" ht="27">
       <c r="A3" s="142" t="s">
         <v>26</v>
       </c>
       <c r="B3" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="57" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="60" t="s">
         <v>86</v>
-      </c>
-      <c r="C3" s="58" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="57" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="60" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27">
       <c r="A4" s="142" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E4" s="60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="28.5">
+    <row r="5" spans="1:6" ht="27">
       <c r="A5" s="142" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E5" s="60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27">
       <c r="A6" s="142" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E6" s="60" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27">
       <c r="A7" s="142" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="60" t="s">
         <v>101</v>
-      </c>
-      <c r="B7" s="57" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" s="57" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" s="60" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="13.9">
@@ -11524,141 +11489,141 @@
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" s="56" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E9" s="56" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F9" s="56" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="27">
       <c r="A10" s="142" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E10" s="60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="27">
       <c r="A11" s="142" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E11" s="60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="27">
       <c r="A12" s="142" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E12" s="60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="27">
       <c r="A13" s="142" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D13" s="57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E13" s="60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="27">
       <c r="A14" s="142" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" s="57" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D14" s="57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E14" s="60" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="27">
       <c r="A15" s="142" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" s="57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D15" s="57" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E15" s="60" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="27">
       <c r="A16" s="142" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B16" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D16" s="57" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E16" s="60" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -11678,77 +11643,77 @@
   <sheetData>
     <row r="1" spans="1:3" ht="13.9">
       <c r="A1" s="145" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B1" s="145" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C1" s="145" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="13.9">
       <c r="A2" s="145" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B2" s="145" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C2" s="145"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -11756,66 +11721,66 @@
     </row>
     <row r="9" spans="1:3" ht="13.9">
       <c r="A9" s="145" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B9" s="146" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C9" s="145"/>
     </row>
-    <row r="10" spans="1:3" ht="28.5">
+    <row r="10" spans="1:3" ht="27">
       <c r="A10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B11" s="54" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -11823,66 +11788,66 @@
     </row>
     <row r="16" spans="1:3" ht="13.9">
       <c r="A16" s="145" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="146" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C16" s="145"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B17" s="54" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B18" s="54" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="27">
       <c r="A19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B19" s="54" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B20" s="54" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B21" s="54" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -11890,66 +11855,66 @@
     </row>
     <row r="23" spans="1:3" ht="13.9">
       <c r="A23" s="145" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B23" s="146" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C23" s="145"/>
     </row>
     <row r="24" spans="1:3" ht="27">
       <c r="A24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B24" s="54" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="27">
       <c r="A25" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B25" s="54" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B26" s="54" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B27" s="54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C27" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B28" s="54" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C28" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -11957,99 +11922,99 @@
     </row>
     <row r="30" spans="1:3" ht="13.9">
       <c r="A30" s="145" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B30" s="146" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C30" s="145"/>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B31" s="54" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C31" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="1:3" s="54" customFormat="1" ht="27">
       <c r="A32" s="54" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B32" s="54" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C32" s="54" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B33" s="54" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C33" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B34" s="54" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C34" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B35" s="54" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C35" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="78.75" customHeight="1">
       <c r="A40" s="62" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B40" s="61" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -12058,6 +12023,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12369,37 +12363,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12407,7 +12372,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2348D59-3426-404A-A0C5-6456F6613EDB}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
